--- a/docs/case_files/CASE_APR.xlsx
+++ b/docs/case_files/CASE_APR.xlsx
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX293"/>
+  <dimension ref="A1:AX296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -42701,6 +42701,402 @@
         <is>
           <t>false</t>
         </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>0.1967333333333333</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.1992</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.2034</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0.1891</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0.1977</v>
+      </c>
+      <c r="G294" t="n">
+        <v>1940969.2344</v>
+      </c>
+      <c r="H294" t="n">
+        <v>48.65836742084942</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0.0002637483333333333</v>
+      </c>
+      <c r="J294" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K294" t="n">
+        <v>0.00050001</v>
+      </c>
+      <c r="L294" t="n">
+        <v>6</v>
+      </c>
+      <c r="M294" t="n">
+        <v>9271101.8532</v>
+      </c>
+      <c r="N294" t="n">
+        <v>46565052</v>
+      </c>
+      <c r="O294" t="n">
+        <v>1</v>
+      </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>-0.7031642390758475</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="n">
+        <v>0</v>
+      </c>
+      <c r="T294" t="n">
+        <v>1.043545329259211</v>
+      </c>
+      <c r="U294" t="n">
+        <v>0.719854330288357</v>
+      </c>
+      <c r="V294" t="n">
+        <v>2.131170973062122</v>
+      </c>
+      <c r="X294" t="n">
+        <v>0.8287160133802213</v>
+      </c>
+      <c r="Y294" t="n">
+        <v>3.541666666666656</v>
+      </c>
+      <c r="Z294" t="n">
+        <v>-21.4594127806563</v>
+      </c>
+      <c r="AA294" t="n">
+        <v>1.9383</v>
+      </c>
+      <c r="AB294" t="n">
+        <v>0.9095</v>
+      </c>
+      <c r="AC294" t="n">
+        <v>0.9661999999999999</v>
+      </c>
+      <c r="AD294" t="n">
+        <v>0.9491000000000001</v>
+      </c>
+      <c r="AK294" t="inlineStr">
+        <is>
+          <t>CoinGecko/BSC+ETH+Monad</t>
+        </is>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>fapi.binance.com klines 1d</t>
+        </is>
+      </c>
+      <c r="AP294" t="inlineStr">
+        <is>
+          <t>fapi.binance.com topPos/topAcc/global/taker</t>
+        </is>
+      </c>
+      <c r="AQ294" t="n">
+        <v>0.3793651697184734</v>
+      </c>
+      <c r="AR294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>0.2039666666666667</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.1976</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0.2079</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0.1962</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0.2078</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1965766.9715</v>
+      </c>
+      <c r="H295" t="n">
+        <v>47.98321707889169</v>
+      </c>
+      <c r="I295" t="n">
+        <v>0.000130415</v>
+      </c>
+      <c r="J295" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K295" t="n">
+        <v>0.00033548</v>
+      </c>
+      <c r="L295" t="n">
+        <v>6</v>
+      </c>
+      <c r="M295" t="n">
+        <v>9095395.372033499</v>
+      </c>
+      <c r="N295" t="n">
+        <v>46019070</v>
+      </c>
+      <c r="O295" t="n">
+        <v>1</v>
+      </c>
+      <c r="P295" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>5.108750632271131</v>
+      </c>
+      <c r="R295" t="n">
+        <v>0</v>
+      </c>
+      <c r="S295" t="n">
+        <v>0</v>
+      </c>
+      <c r="T295" t="n">
+        <v>1.023767995276133</v>
+      </c>
+      <c r="U295" t="n">
+        <v>0.7520151736142805</v>
+      </c>
+      <c r="V295" t="n">
+        <v>1.557080220850926</v>
+      </c>
+      <c r="W295" t="n">
+        <v>1.800943440287703</v>
+      </c>
+      <c r="X295" t="n">
+        <v>1.255536454646577</v>
+      </c>
+      <c r="Y295" t="n">
+        <v>-1.062786978279934</v>
+      </c>
+      <c r="Z295" t="n">
+        <v>35.41506322155031</v>
+      </c>
+      <c r="AA295" t="n">
+        <v>1.9177</v>
+      </c>
+      <c r="AB295" t="n">
+        <v>1.2316</v>
+      </c>
+      <c r="AC295" t="n">
+        <v>1.2416</v>
+      </c>
+      <c r="AD295" t="n">
+        <v>0.9226</v>
+      </c>
+      <c r="AK295" t="inlineStr">
+        <is>
+          <t>CoinGecko/BSC+ETH+Monad</t>
+        </is>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>fapi.binance.com klines 1d</t>
+        </is>
+      </c>
+      <c r="AP295" t="inlineStr">
+        <is>
+          <t>fapi.binance.com topPos/topAcc/global/taker</t>
+        </is>
+      </c>
+      <c r="AQ295" t="n">
+        <v>0.3133809525063222</v>
+      </c>
+      <c r="AR295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>0.4822333333333333</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.2076</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0.6325</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0.6074000000000001</v>
+      </c>
+      <c r="G296" t="n">
+        <v>903339470.6586699</v>
+      </c>
+      <c r="H296" t="n">
+        <v>51.95693523323135</v>
+      </c>
+      <c r="I296" t="n">
+        <v>0.0002265583333333333</v>
+      </c>
+      <c r="J296" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K296" t="n">
+        <v>0.00060334</v>
+      </c>
+      <c r="L296" t="n">
+        <v>6</v>
+      </c>
+      <c r="M296" t="n">
+        <v>9689917.191729</v>
+      </c>
+      <c r="N296" t="n">
+        <v>46642515</v>
+      </c>
+      <c r="O296" t="n">
+        <v>1</v>
+      </c>
+      <c r="P296" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>192.3002887391723</v>
+      </c>
+      <c r="R296" t="n">
+        <v>0</v>
+      </c>
+      <c r="S296" t="n">
+        <v>0</v>
+      </c>
+      <c r="T296" t="n">
+        <v>1.090686736749325</v>
+      </c>
+      <c r="U296" t="n">
+        <v>345.5775779677718</v>
+      </c>
+      <c r="V296" t="n">
+        <v>1.498530463102709</v>
+      </c>
+      <c r="W296" t="n">
+        <v>1.688970588235294</v>
+      </c>
+      <c r="X296" t="n">
+        <v>1.122109158186864</v>
+      </c>
+      <c r="Y296" t="n">
+        <v>-2.672444925966045</v>
+      </c>
+      <c r="Z296" t="n">
+        <v>38.41671247938427</v>
+      </c>
+      <c r="AA296" t="n">
+        <v>1.8865</v>
+      </c>
+      <c r="AB296" t="n">
+        <v>1.2589</v>
+      </c>
+      <c r="AC296" t="n">
+        <v>1.3343</v>
+      </c>
+      <c r="AD296" t="n">
+        <v>1.0745</v>
+      </c>
+      <c r="AK296" t="inlineStr">
+        <is>
+          <t>CoinGecko/BSC+ETH+Monad</t>
+        </is>
+      </c>
+      <c r="AO296" t="inlineStr">
+        <is>
+          <t>fapi.binance.com klines 1d</t>
+        </is>
+      </c>
+      <c r="AP296" t="inlineStr">
+        <is>
+          <t>fapi.binance.com topPos/topAcc/global/taker</t>
+        </is>
+      </c>
+      <c r="AQ296" t="n">
+        <v>0.5366456643582297</v>
+      </c>
+      <c r="AR296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX296" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/case_files/CASE_APR.xlsx
+++ b/docs/case_files/CASE_APR.xlsx
@@ -36438,9 +36438,11 @@
       <c r="AD254" s="14" t="n">
         <v>0.9496550973326324</v>
       </c>
-      <c r="AE254" s="14" t="inlineStr"/>
-      <c r="AF254" s="14" t="inlineStr"/>
-      <c r="AG254" s="14" t="inlineStr"/>
+      <c r="AE254" s="14" t="n">
+        <v>120860.37</v>
+      </c>
+      <c r="AF254" s="14" t="n"/>
+      <c r="AG254" s="14" t="n"/>
       <c r="AH254" s="14" t="inlineStr"/>
       <c r="AI254" s="14" t="inlineStr">
         <is>
@@ -36594,9 +36596,11 @@
       <c r="AD255" s="14" t="n">
         <v>0.8142457120034781</v>
       </c>
-      <c r="AE255" s="14" t="inlineStr"/>
-      <c r="AF255" s="14" t="inlineStr"/>
-      <c r="AG255" s="14" t="inlineStr"/>
+      <c r="AE255" s="14" t="n">
+        <v>98680.88</v>
+      </c>
+      <c r="AF255" s="14" t="n"/>
+      <c r="AG255" s="14" t="n"/>
       <c r="AH255" s="14" t="inlineStr"/>
       <c r="AI255" s="14" t="inlineStr">
         <is>
@@ -36750,9 +36754,11 @@
       <c r="AD256" s="14" t="n">
         <v>0.9584829397650404</v>
       </c>
-      <c r="AE256" s="14" t="inlineStr"/>
-      <c r="AF256" s="14" t="inlineStr"/>
-      <c r="AG256" s="14" t="inlineStr"/>
+      <c r="AE256" s="14" t="n">
+        <v>43791.69</v>
+      </c>
+      <c r="AF256" s="14" t="n"/>
+      <c r="AG256" s="14" t="n"/>
       <c r="AH256" s="14" t="inlineStr"/>
       <c r="AI256" s="14" t="inlineStr">
         <is>
@@ -36906,9 +36912,11 @@
       <c r="AD257" s="14" t="n">
         <v>0.8590722824294629</v>
       </c>
-      <c r="AE257" s="14" t="inlineStr"/>
-      <c r="AF257" s="14" t="inlineStr"/>
-      <c r="AG257" s="14" t="inlineStr"/>
+      <c r="AE257" s="14" t="n">
+        <v>20825.05</v>
+      </c>
+      <c r="AF257" s="14" t="n"/>
+      <c r="AG257" s="14" t="n"/>
       <c r="AH257" s="14" t="inlineStr"/>
       <c r="AI257" s="14" t="inlineStr">
         <is>
@@ -37062,9 +37070,11 @@
       <c r="AD258" s="14" t="n">
         <v>1.07634354892753</v>
       </c>
-      <c r="AE258" s="14" t="inlineStr"/>
-      <c r="AF258" s="14" t="inlineStr"/>
-      <c r="AG258" s="14" t="inlineStr"/>
+      <c r="AE258" s="14" t="n">
+        <v>72029.92</v>
+      </c>
+      <c r="AF258" s="14" t="n"/>
+      <c r="AG258" s="14" t="n"/>
       <c r="AH258" s="14" t="inlineStr"/>
       <c r="AI258" s="14" t="inlineStr">
         <is>
@@ -37222,9 +37232,11 @@
       <c r="AD259" s="14" t="n">
         <v>0.9344021074234776</v>
       </c>
-      <c r="AE259" s="14" t="inlineStr"/>
-      <c r="AF259" s="14" t="inlineStr"/>
-      <c r="AG259" s="14" t="inlineStr"/>
+      <c r="AE259" s="14" t="n">
+        <v>46588.05</v>
+      </c>
+      <c r="AF259" s="14" t="n"/>
+      <c r="AG259" s="14" t="n"/>
       <c r="AH259" s="14" t="inlineStr"/>
       <c r="AI259" s="14" t="inlineStr">
         <is>
@@ -37378,9 +37390,11 @@
       <c r="AD260" s="14" t="n">
         <v>0.9753367267882268</v>
       </c>
-      <c r="AE260" s="14" t="inlineStr"/>
-      <c r="AF260" s="14" t="inlineStr"/>
-      <c r="AG260" s="14" t="inlineStr"/>
+      <c r="AE260" s="14" t="n">
+        <v>36660.16</v>
+      </c>
+      <c r="AF260" s="14" t="n"/>
+      <c r="AG260" s="14" t="n"/>
       <c r="AH260" s="14" t="inlineStr"/>
       <c r="AI260" s="14" t="inlineStr">
         <is>
@@ -37534,9 +37548,11 @@
       <c r="AD261" s="14" t="n">
         <v>0.949664800041624</v>
       </c>
-      <c r="AE261" s="14" t="inlineStr"/>
-      <c r="AF261" s="14" t="inlineStr"/>
-      <c r="AG261" s="14" t="inlineStr"/>
+      <c r="AE261" s="14" t="n">
+        <v>42527.9</v>
+      </c>
+      <c r="AF261" s="14" t="n"/>
+      <c r="AG261" s="14" t="n"/>
       <c r="AH261" s="14" t="inlineStr"/>
       <c r="AI261" s="14" t="inlineStr">
         <is>
@@ -37690,9 +37706,11 @@
       <c r="AD262" s="14" t="n">
         <v>0.8166694113025433</v>
       </c>
-      <c r="AE262" s="14" t="inlineStr"/>
-      <c r="AF262" s="14" t="inlineStr"/>
-      <c r="AG262" s="14" t="inlineStr"/>
+      <c r="AE262" s="14" t="n">
+        <v>18799.51</v>
+      </c>
+      <c r="AF262" s="14" t="n"/>
+      <c r="AG262" s="14" t="n"/>
       <c r="AH262" s="14" t="inlineStr"/>
       <c r="AI262" s="14" t="inlineStr">
         <is>
@@ -37846,9 +37864,11 @@
       <c r="AD263" s="14" t="n">
         <v>1.059999680578949</v>
       </c>
-      <c r="AE263" s="14" t="inlineStr"/>
-      <c r="AF263" s="14" t="inlineStr"/>
-      <c r="AG263" s="14" t="inlineStr"/>
+      <c r="AE263" s="14" t="n">
+        <v>17036.21</v>
+      </c>
+      <c r="AF263" s="14" t="n"/>
+      <c r="AG263" s="14" t="n"/>
       <c r="AH263" s="14" t="inlineStr"/>
       <c r="AI263" s="14" t="inlineStr">
         <is>
@@ -38002,9 +38022,11 @@
       <c r="AD264" s="14" t="n">
         <v>0.9419084735050482</v>
       </c>
-      <c r="AE264" s="14" t="inlineStr"/>
-      <c r="AF264" s="14" t="inlineStr"/>
-      <c r="AG264" s="14" t="inlineStr"/>
+      <c r="AE264" s="14" t="n">
+        <v>61301.97</v>
+      </c>
+      <c r="AF264" s="14" t="n"/>
+      <c r="AG264" s="14" t="n"/>
       <c r="AH264" s="14" t="inlineStr"/>
       <c r="AI264" s="14" t="inlineStr">
         <is>
@@ -38162,9 +38184,13 @@
       <c r="AD265" s="14" t="n">
         <v>1.027488323272699</v>
       </c>
-      <c r="AE265" s="14" t="inlineStr"/>
-      <c r="AF265" s="14" t="inlineStr"/>
-      <c r="AG265" s="14" t="inlineStr"/>
+      <c r="AE265" s="14" t="n">
+        <v>30678.18</v>
+      </c>
+      <c r="AF265" s="14" t="n"/>
+      <c r="AG265" s="14" t="n">
+        <v>0.003231</v>
+      </c>
       <c r="AH265" s="14" t="inlineStr"/>
       <c r="AI265" s="14" t="inlineStr">
         <is>
@@ -38322,9 +38348,13 @@
       <c r="AD266" s="14" t="n">
         <v>0.905838599867248</v>
       </c>
-      <c r="AE266" s="14" t="inlineStr"/>
-      <c r="AF266" s="14" t="inlineStr"/>
-      <c r="AG266" s="14" t="inlineStr"/>
+      <c r="AE266" s="14" t="n">
+        <v>53610.76</v>
+      </c>
+      <c r="AF266" s="14" t="n"/>
+      <c r="AG266" s="14" t="n">
+        <v>0.005216</v>
+      </c>
       <c r="AH266" s="14" t="inlineStr"/>
       <c r="AI266" s="14" t="inlineStr">
         <is>
@@ -38482,9 +38512,13 @@
       <c r="AD267" s="14" t="n">
         <v>0.9635347183991276</v>
       </c>
-      <c r="AE267" s="14" t="inlineStr"/>
-      <c r="AF267" s="14" t="inlineStr"/>
-      <c r="AG267" s="14" t="inlineStr"/>
+      <c r="AE267" s="14" t="n">
+        <v>63867.37</v>
+      </c>
+      <c r="AF267" s="14" t="n"/>
+      <c r="AG267" s="14" t="n">
+        <v>0.0068</v>
+      </c>
       <c r="AH267" s="14" t="inlineStr"/>
       <c r="AI267" s="14" t="inlineStr">
         <is>
@@ -38642,9 +38676,13 @@
       <c r="AD268" s="14" t="n">
         <v>0.9605577222110836</v>
       </c>
-      <c r="AE268" s="14" t="inlineStr"/>
-      <c r="AF268" s="14" t="inlineStr"/>
-      <c r="AG268" s="14" t="inlineStr"/>
+      <c r="AE268" s="14" t="n">
+        <v>47367.93</v>
+      </c>
+      <c r="AF268" s="14" t="n"/>
+      <c r="AG268" s="14" t="n">
+        <v>0.00501</v>
+      </c>
       <c r="AH268" s="14" t="inlineStr"/>
       <c r="AI268" s="14" t="inlineStr">
         <is>
@@ -38802,9 +38840,13 @@
       <c r="AD269" s="14" t="n">
         <v>1.200131229264558</v>
       </c>
-      <c r="AE269" s="14" t="inlineStr"/>
-      <c r="AF269" s="14" t="inlineStr"/>
-      <c r="AG269" s="14" t="inlineStr"/>
+      <c r="AE269" s="14" t="n">
+        <v>34199.73</v>
+      </c>
+      <c r="AF269" s="14" t="n"/>
+      <c r="AG269" s="14" t="n">
+        <v>0.003629</v>
+      </c>
       <c r="AH269" s="14" t="inlineStr"/>
       <c r="AI269" s="14" t="inlineStr">
         <is>
@@ -38962,9 +39004,13 @@
       <c r="AD270" s="14" t="n">
         <v>0.9868165960607348</v>
       </c>
-      <c r="AE270" s="14" t="inlineStr"/>
-      <c r="AF270" s="14" t="inlineStr"/>
-      <c r="AG270" s="14" t="inlineStr"/>
+      <c r="AE270" s="14" t="n">
+        <v>40192.76</v>
+      </c>
+      <c r="AF270" s="14" t="n"/>
+      <c r="AG270" s="14" t="n">
+        <v>0.004135</v>
+      </c>
       <c r="AH270" s="14" t="inlineStr"/>
       <c r="AI270" s="14" t="inlineStr">
         <is>
@@ -39122,9 +39168,13 @@
       <c r="AD271" s="14" t="n">
         <v>1.013091468576515</v>
       </c>
-      <c r="AE271" s="14" t="inlineStr"/>
-      <c r="AF271" s="14" t="inlineStr"/>
-      <c r="AG271" s="14" t="inlineStr"/>
+      <c r="AE271" s="14" t="n">
+        <v>23984.96</v>
+      </c>
+      <c r="AF271" s="14" t="n"/>
+      <c r="AG271" s="14" t="n">
+        <v>0.002558</v>
+      </c>
       <c r="AH271" s="14" t="inlineStr"/>
       <c r="AI271" s="14" t="inlineStr">
         <is>
@@ -39284,9 +39334,13 @@
       <c r="AD272" s="14" t="n">
         <v>0.85381705643743</v>
       </c>
-      <c r="AE272" s="14" t="inlineStr"/>
-      <c r="AF272" s="14" t="inlineStr"/>
-      <c r="AG272" s="14" t="inlineStr"/>
+      <c r="AE272" s="14" t="n">
+        <v>38075.58</v>
+      </c>
+      <c r="AF272" s="14" t="n"/>
+      <c r="AG272" s="14" t="n">
+        <v>0.003959</v>
+      </c>
       <c r="AH272" s="14" t="inlineStr"/>
       <c r="AI272" s="14" t="inlineStr">
         <is>
@@ -39446,9 +39500,13 @@
       <c r="AD273" s="14" t="n">
         <v>0.9158730737407392</v>
       </c>
-      <c r="AE273" s="14" t="inlineStr"/>
-      <c r="AF273" s="14" t="inlineStr"/>
-      <c r="AG273" s="14" t="inlineStr"/>
+      <c r="AE273" s="14" t="n">
+        <v>16946.91</v>
+      </c>
+      <c r="AF273" s="14" t="n"/>
+      <c r="AG273" s="14" t="n">
+        <v>0.001776</v>
+      </c>
       <c r="AH273" s="14" t="inlineStr"/>
       <c r="AI273" s="14" t="inlineStr">
         <is>
@@ -39608,9 +39666,13 @@
       <c r="AD274" s="14" t="n">
         <v>0.8756275490872794</v>
       </c>
-      <c r="AE274" s="14" t="inlineStr"/>
-      <c r="AF274" s="14" t="inlineStr"/>
-      <c r="AG274" s="14" t="inlineStr"/>
+      <c r="AE274" s="14" t="n">
+        <v>29644.95</v>
+      </c>
+      <c r="AF274" s="14" t="n"/>
+      <c r="AG274" s="14" t="n">
+        <v>0.003132</v>
+      </c>
       <c r="AH274" s="14" t="inlineStr"/>
       <c r="AI274" s="14" t="inlineStr">
         <is>
@@ -39772,9 +39834,13 @@
       <c r="AD275" s="14" t="n">
         <v>0.7407839683808324</v>
       </c>
-      <c r="AE275" s="14" t="inlineStr"/>
-      <c r="AF275" s="14" t="inlineStr"/>
-      <c r="AG275" s="14" t="inlineStr"/>
+      <c r="AE275" s="14" t="n">
+        <v>21265.7</v>
+      </c>
+      <c r="AF275" s="14" t="n"/>
+      <c r="AG275" s="14" t="n">
+        <v>0.002266</v>
+      </c>
       <c r="AH275" s="14" t="inlineStr"/>
       <c r="AI275" s="14" t="inlineStr">
         <is>
@@ -39936,9 +40002,13 @@
       <c r="AD276" s="14" t="n">
         <v>0.9041377382073656</v>
       </c>
-      <c r="AE276" s="14" t="inlineStr"/>
-      <c r="AF276" s="14" t="inlineStr"/>
-      <c r="AG276" s="14" t="inlineStr"/>
+      <c r="AE276" s="14" t="n">
+        <v>108217.22</v>
+      </c>
+      <c r="AF276" s="14" t="n"/>
+      <c r="AG276" s="14" t="n">
+        <v>0.012025</v>
+      </c>
       <c r="AH276" s="14" t="inlineStr"/>
       <c r="AI276" s="14" t="inlineStr">
         <is>
@@ -40082,9 +40152,13 @@
       <c r="AB277" s="14" t="inlineStr"/>
       <c r="AC277" s="14" t="inlineStr"/>
       <c r="AD277" s="14" t="inlineStr"/>
-      <c r="AE277" s="14" t="inlineStr"/>
-      <c r="AF277" s="14" t="inlineStr"/>
-      <c r="AG277" s="14" t="inlineStr"/>
+      <c r="AE277" s="14" t="n">
+        <v>134453.78</v>
+      </c>
+      <c r="AF277" s="14" t="n"/>
+      <c r="AG277" s="14" t="n">
+        <v>0.014809</v>
+      </c>
       <c r="AH277" s="14" t="inlineStr"/>
       <c r="AI277" s="14" t="inlineStr">
         <is>
@@ -40228,9 +40302,13 @@
       <c r="AB278" s="14" t="inlineStr"/>
       <c r="AC278" s="14" t="inlineStr"/>
       <c r="AD278" s="14" t="inlineStr"/>
-      <c r="AE278" s="14" t="inlineStr"/>
-      <c r="AF278" s="14" t="inlineStr"/>
-      <c r="AG278" s="14" t="inlineStr"/>
+      <c r="AE278" s="14" t="n">
+        <v>57224.83</v>
+      </c>
+      <c r="AF278" s="14" t="n"/>
+      <c r="AG278" s="14" t="n">
+        <v>0.006043</v>
+      </c>
       <c r="AH278" s="14" t="inlineStr"/>
       <c r="AI278" s="14" t="inlineStr">
         <is>
@@ -40374,9 +40452,13 @@
       <c r="AB279" s="14" t="inlineStr"/>
       <c r="AC279" s="14" t="inlineStr"/>
       <c r="AD279" s="14" t="inlineStr"/>
-      <c r="AE279" s="14" t="inlineStr"/>
-      <c r="AF279" s="14" t="inlineStr"/>
-      <c r="AG279" s="14" t="inlineStr"/>
+      <c r="AE279" s="14" t="n">
+        <v>34551.04</v>
+      </c>
+      <c r="AF279" s="14" t="n"/>
+      <c r="AG279" s="14" t="n">
+        <v>0.003725</v>
+      </c>
       <c r="AH279" s="14" t="inlineStr"/>
       <c r="AI279" s="14" t="inlineStr">
         <is>
@@ -40532,9 +40614,13 @@
       <c r="AD280" s="14" t="n">
         <v>0.8628</v>
       </c>
-      <c r="AE280" s="14" t="inlineStr"/>
-      <c r="AF280" s="14" t="inlineStr"/>
-      <c r="AG280" s="14" t="inlineStr"/>
+      <c r="AE280" s="14" t="n">
+        <v>43854.05</v>
+      </c>
+      <c r="AF280" s="14" t="n"/>
+      <c r="AG280" s="14" t="n">
+        <v>0.004853</v>
+      </c>
       <c r="AH280" s="14" t="inlineStr"/>
       <c r="AI280" s="14" t="inlineStr">
         <is>
@@ -40690,9 +40776,13 @@
       <c r="AD281" s="14" t="n">
         <v>0.9897</v>
       </c>
-      <c r="AE281" s="14" t="inlineStr"/>
-      <c r="AF281" s="14" t="inlineStr"/>
-      <c r="AG281" s="14" t="inlineStr"/>
+      <c r="AE281" s="14" t="n">
+        <v>31952.26</v>
+      </c>
+      <c r="AF281" s="14" t="n"/>
+      <c r="AG281" s="14" t="n">
+        <v>0.003559</v>
+      </c>
       <c r="AH281" s="14" t="inlineStr"/>
       <c r="AI281" s="14" t="inlineStr">
         <is>
@@ -40848,9 +40938,13 @@
       <c r="AD282" s="14" t="n">
         <v>0.9313</v>
       </c>
-      <c r="AE282" s="14" t="inlineStr"/>
-      <c r="AF282" s="14" t="inlineStr"/>
-      <c r="AG282" s="14" t="inlineStr"/>
+      <c r="AE282" s="14" t="n">
+        <v>32456.37</v>
+      </c>
+      <c r="AF282" s="14" t="n"/>
+      <c r="AG282" s="14" t="n">
+        <v>0.003691</v>
+      </c>
       <c r="AH282" s="14" t="inlineStr"/>
       <c r="AI282" s="14" t="inlineStr">
         <is>
@@ -41010,9 +41104,13 @@
       <c r="AD283" s="14" t="n">
         <v>1.0004</v>
       </c>
-      <c r="AE283" s="14" t="inlineStr"/>
-      <c r="AF283" s="14" t="inlineStr"/>
-      <c r="AG283" s="14" t="inlineStr"/>
+      <c r="AE283" s="14" t="n">
+        <v>16646.09</v>
+      </c>
+      <c r="AF283" s="14" t="n"/>
+      <c r="AG283" s="14" t="n">
+        <v>0.001869</v>
+      </c>
       <c r="AH283" s="14" t="inlineStr"/>
       <c r="AI283" s="14" t="inlineStr">
         <is>
@@ -41176,9 +41274,13 @@
       <c r="AD284" s="14" t="n">
         <v>1.0206</v>
       </c>
-      <c r="AE284" s="14" t="inlineStr"/>
-      <c r="AF284" s="14" t="inlineStr"/>
-      <c r="AG284" s="14" t="inlineStr"/>
+      <c r="AE284" s="14" t="n">
+        <v>19251.05</v>
+      </c>
+      <c r="AF284" s="14" t="n"/>
+      <c r="AG284" s="14" t="n">
+        <v>0.002188</v>
+      </c>
       <c r="AH284" s="14" t="inlineStr"/>
       <c r="AI284" s="14" t="inlineStr">
         <is>
@@ -41340,9 +41442,13 @@
       <c r="AD285" s="14" t="n">
         <v>0.9828</v>
       </c>
-      <c r="AE285" s="14" t="inlineStr"/>
-      <c r="AF285" s="14" t="inlineStr"/>
-      <c r="AG285" s="14" t="inlineStr"/>
+      <c r="AE285" s="14" t="n">
+        <v>37908.68</v>
+      </c>
+      <c r="AF285" s="14" t="n"/>
+      <c r="AG285" s="14" t="n">
+        <v>0.004278</v>
+      </c>
       <c r="AH285" s="14" t="inlineStr"/>
       <c r="AI285" s="14" t="inlineStr">
         <is>
@@ -41504,9 +41610,13 @@
       <c r="AD286" s="14" t="n">
         <v>0.9375</v>
       </c>
-      <c r="AE286" s="14" t="inlineStr"/>
-      <c r="AF286" s="14" t="inlineStr"/>
-      <c r="AG286" s="14" t="inlineStr"/>
+      <c r="AE286" s="14" t="n">
+        <v>56878.22</v>
+      </c>
+      <c r="AF286" s="14" t="n"/>
+      <c r="AG286" s="14" t="n">
+        <v>0.005207</v>
+      </c>
       <c r="AH286" s="14" t="inlineStr"/>
       <c r="AI286" s="14" t="inlineStr">
         <is>
@@ -41668,9 +41778,13 @@
       <c r="AD287" s="14" t="n">
         <v>1.0287</v>
       </c>
-      <c r="AE287" s="14" t="inlineStr"/>
-      <c r="AF287" s="14" t="inlineStr"/>
-      <c r="AG287" s="14" t="inlineStr"/>
+      <c r="AE287" s="14" t="n">
+        <v>21515.26</v>
+      </c>
+      <c r="AF287" s="14" t="n"/>
+      <c r="AG287" s="14" t="n">
+        <v>0.002311</v>
+      </c>
       <c r="AH287" s="14" t="inlineStr"/>
       <c r="AI287" s="14" t="inlineStr">
         <is>
@@ -41836,9 +41950,13 @@
       <c r="AD288" s="14" t="n">
         <v>0.924</v>
       </c>
-      <c r="AE288" s="14" t="inlineStr"/>
-      <c r="AF288" s="14" t="inlineStr"/>
-      <c r="AG288" s="14" t="inlineStr"/>
+      <c r="AE288" s="14" t="n">
+        <v>16216.17</v>
+      </c>
+      <c r="AF288" s="14" t="n"/>
+      <c r="AG288" s="14" t="n">
+        <v>0.001838</v>
+      </c>
       <c r="AH288" s="14" t="inlineStr"/>
       <c r="AI288" s="14" t="inlineStr">
         <is>
@@ -42000,9 +42118,13 @@
       <c r="AD289" s="14" t="n">
         <v>0.9426</v>
       </c>
-      <c r="AE289" s="14" t="inlineStr"/>
-      <c r="AF289" s="14" t="inlineStr"/>
-      <c r="AG289" s="14" t="inlineStr"/>
+      <c r="AE289" s="14" t="n">
+        <v>29733.33</v>
+      </c>
+      <c r="AF289" s="14" t="n"/>
+      <c r="AG289" s="14" t="n">
+        <v>0.003599</v>
+      </c>
       <c r="AH289" s="14" t="inlineStr"/>
       <c r="AI289" s="14" t="inlineStr">
         <is>
@@ -42168,9 +42290,13 @@
       <c r="AD290" s="14" t="n">
         <v>1.0982</v>
       </c>
-      <c r="AE290" s="14" t="inlineStr"/>
-      <c r="AF290" s="14" t="inlineStr"/>
-      <c r="AG290" s="14" t="inlineStr"/>
+      <c r="AE290" s="14" t="n">
+        <v>50220.07</v>
+      </c>
+      <c r="AF290" s="14" t="n"/>
+      <c r="AG290" s="14" t="n">
+        <v>0.005714</v>
+      </c>
       <c r="AH290" s="14" t="inlineStr"/>
       <c r="AI290" s="14" t="inlineStr">
         <is>
@@ -42340,9 +42466,13 @@
       <c r="AD291" s="14" t="n">
         <v>1.0413</v>
       </c>
-      <c r="AE291" s="14" t="inlineStr"/>
-      <c r="AF291" s="14" t="inlineStr"/>
-      <c r="AG291" s="14" t="inlineStr"/>
+      <c r="AE291" s="14" t="n">
+        <v>75229.63</v>
+      </c>
+      <c r="AF291" s="14" t="n"/>
+      <c r="AG291" s="14" t="n">
+        <v>0.008500000000000001</v>
+      </c>
       <c r="AH291" s="14" t="inlineStr"/>
       <c r="AI291" s="14" t="inlineStr">
         <is>
@@ -42486,9 +42616,13 @@
       <c r="AB292" s="14" t="inlineStr"/>
       <c r="AC292" s="14" t="inlineStr"/>
       <c r="AD292" s="14" t="inlineStr"/>
-      <c r="AE292" s="14" t="inlineStr"/>
-      <c r="AF292" s="14" t="inlineStr"/>
-      <c r="AG292" s="14" t="inlineStr"/>
+      <c r="AE292" s="14" t="n">
+        <v>49569.36</v>
+      </c>
+      <c r="AF292" s="14" t="n"/>
+      <c r="AG292" s="14" t="n">
+        <v>0.004976</v>
+      </c>
       <c r="AH292" s="14" t="inlineStr"/>
       <c r="AI292" s="14" t="inlineStr">
         <is>
@@ -42632,9 +42766,13 @@
       <c r="AB293" s="14" t="inlineStr"/>
       <c r="AC293" s="14" t="inlineStr"/>
       <c r="AD293" s="14" t="inlineStr"/>
-      <c r="AE293" s="14" t="inlineStr"/>
-      <c r="AF293" s="14" t="inlineStr"/>
-      <c r="AG293" s="14" t="inlineStr"/>
+      <c r="AE293" s="14" t="n">
+        <v>71923.63</v>
+      </c>
+      <c r="AF293" s="14" t="n"/>
+      <c r="AG293" s="14" t="n">
+        <v>0.007432</v>
+      </c>
       <c r="AH293" s="14" t="inlineStr"/>
       <c r="AI293" s="14" t="inlineStr">
         <is>
@@ -42793,6 +42931,12 @@
       <c r="AD294" t="n">
         <v>0.9491000000000001</v>
       </c>
+      <c r="AE294" t="n">
+        <v>31251.84</v>
+      </c>
+      <c r="AG294" t="n">
+        <v>0.003371</v>
+      </c>
       <c r="AK294" t="inlineStr">
         <is>
           <t>CoinGecko/BSC+ETH+Monad</t>
@@ -42926,6 +43070,12 @@
       <c r="AD295" t="n">
         <v>0.9226</v>
       </c>
+      <c r="AE295" t="n">
+        <v>26487.55</v>
+      </c>
+      <c r="AG295" t="n">
+        <v>0.002912</v>
+      </c>
       <c r="AK295" t="inlineStr">
         <is>
           <t>CoinGecko/BSC+ETH+Monad</t>
@@ -43058,6 +43208,12 @@
       </c>
       <c r="AD296" t="n">
         <v>1.0745</v>
+      </c>
+      <c r="AE296" t="n">
+        <v>3928680.4</v>
+      </c>
+      <c r="AG296" t="n">
+        <v>0.40544</v>
       </c>
       <c r="AK296" t="inlineStr">
         <is>

--- a/docs/case_files/CASE_APR.xlsx
+++ b/docs/case_files/CASE_APR.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>APRUSDT</t>
+          <t>APR</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>fullyDelisted=False, offsell=False, offline=False</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Co luc gom khong? Neu co: gom tu bao gio, bao nhieu (§3), pha nao vong doi? Neu khong: farm hay xac hay ban-vua-lau?</t>
+          <t>Cau hoi case: TBD — operator dien</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX296"/>
+  <dimension ref="A1:AX300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -31737,25 +31737,15 @@
       <c r="U224" s="14" t="n">
         <v>1.16</v>
       </c>
-      <c r="V224" s="14" t="n">
-        <v>1.3622</v>
-      </c>
+      <c r="V224" s="14" t="inlineStr"/>
       <c r="W224" s="14" t="inlineStr"/>
       <c r="X224" s="14" t="inlineStr"/>
       <c r="Y224" s="14" t="inlineStr"/>
       <c r="Z224" s="14" t="inlineStr"/>
-      <c r="AA224" s="14" t="n">
-        <v>2.2645</v>
-      </c>
-      <c r="AB224" s="14" t="n">
-        <v>1.6624</v>
-      </c>
-      <c r="AC224" s="14" t="n">
-        <v>1.517</v>
-      </c>
-      <c r="AD224" s="14" t="n">
-        <v>0.9445925844908096</v>
-      </c>
+      <c r="AA224" s="14" t="inlineStr"/>
+      <c r="AB224" s="14" t="inlineStr"/>
+      <c r="AC224" s="14" t="inlineStr"/>
+      <c r="AD224" s="14" t="inlineStr"/>
       <c r="AE224" s="14" t="inlineStr"/>
       <c r="AF224" s="14" t="inlineStr"/>
       <c r="AG224" s="14" t="inlineStr"/>
@@ -31793,7 +31783,7 @@
       </c>
       <c r="AP224" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ224" s="14" t="inlineStr"/>
@@ -31885,25 +31875,15 @@
       <c r="U225" s="14" t="n">
         <v>10.14</v>
       </c>
-      <c r="V225" s="14" t="n">
-        <v>1.1699</v>
-      </c>
+      <c r="V225" s="14" t="inlineStr"/>
       <c r="W225" s="14" t="inlineStr"/>
       <c r="X225" s="14" t="inlineStr"/>
       <c r="Y225" s="14" t="inlineStr"/>
       <c r="Z225" s="14" t="inlineStr"/>
-      <c r="AA225" s="14" t="n">
-        <v>2.2741</v>
-      </c>
-      <c r="AB225" s="14" t="n">
-        <v>1.9438</v>
-      </c>
-      <c r="AC225" s="14" t="n">
-        <v>1.7902</v>
-      </c>
-      <c r="AD225" s="14" t="n">
-        <v>1.05714238536769</v>
-      </c>
+      <c r="AA225" s="14" t="inlineStr"/>
+      <c r="AB225" s="14" t="inlineStr"/>
+      <c r="AC225" s="14" t="inlineStr"/>
+      <c r="AD225" s="14" t="inlineStr"/>
       <c r="AE225" s="14" t="inlineStr"/>
       <c r="AF225" s="14" t="inlineStr"/>
       <c r="AG225" s="14" t="inlineStr"/>
@@ -31941,7 +31921,7 @@
       </c>
       <c r="AP225" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ225" s="14" t="inlineStr"/>
@@ -32033,27 +32013,15 @@
       <c r="U226" s="14" t="n">
         <v>22.36</v>
       </c>
-      <c r="V226" s="14" t="n">
-        <v>2.1117</v>
-      </c>
-      <c r="W226" s="14" t="n">
-        <v>1.4448</v>
-      </c>
+      <c r="V226" s="14" t="inlineStr"/>
+      <c r="W226" s="14" t="inlineStr"/>
       <c r="X226" s="14" t="inlineStr"/>
       <c r="Y226" s="14" t="inlineStr"/>
       <c r="Z226" s="14" t="inlineStr"/>
-      <c r="AA226" s="14" t="n">
-        <v>2.1269</v>
-      </c>
-      <c r="AB226" s="14" t="n">
-        <v>1.0072</v>
-      </c>
-      <c r="AC226" s="14" t="n">
-        <v>0.9857</v>
-      </c>
-      <c r="AD226" s="14" t="n">
-        <v>1.00888068951869</v>
-      </c>
+      <c r="AA226" s="14" t="inlineStr"/>
+      <c r="AB226" s="14" t="inlineStr"/>
+      <c r="AC226" s="14" t="inlineStr"/>
+      <c r="AD226" s="14" t="inlineStr"/>
       <c r="AE226" s="14" t="inlineStr"/>
       <c r="AF226" s="14" t="inlineStr"/>
       <c r="AG226" s="14" t="inlineStr"/>
@@ -32091,7 +32059,7 @@
       </c>
       <c r="AP226" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ226" s="14" t="inlineStr"/>
@@ -32187,31 +32155,15 @@
       <c r="U227" s="14" t="n">
         <v>3.64</v>
       </c>
-      <c r="V227" s="14" t="n">
-        <v>2.0267</v>
-      </c>
-      <c r="W227" s="14" t="n">
-        <v>1.633</v>
-      </c>
+      <c r="V227" s="14" t="inlineStr"/>
+      <c r="W227" s="14" t="inlineStr"/>
       <c r="X227" s="14" t="inlineStr"/>
-      <c r="Y227" s="14" t="n">
-        <v>-5.01</v>
-      </c>
-      <c r="Z227" s="14" t="n">
-        <v>-36.15</v>
-      </c>
-      <c r="AA227" s="14" t="n">
-        <v>2.1511</v>
-      </c>
-      <c r="AB227" s="14" t="n">
-        <v>1.0614</v>
-      </c>
-      <c r="AC227" s="14" t="n">
-        <v>1.0458</v>
-      </c>
-      <c r="AD227" s="14" t="n">
-        <v>0.9988521323609232</v>
-      </c>
+      <c r="Y227" s="14" t="inlineStr"/>
+      <c r="Z227" s="14" t="inlineStr"/>
+      <c r="AA227" s="14" t="inlineStr"/>
+      <c r="AB227" s="14" t="inlineStr"/>
+      <c r="AC227" s="14" t="inlineStr"/>
+      <c r="AD227" s="14" t="inlineStr"/>
       <c r="AE227" s="14" t="inlineStr"/>
       <c r="AF227" s="14" t="inlineStr"/>
       <c r="AG227" s="14" t="inlineStr"/>
@@ -32249,7 +32201,7 @@
       </c>
       <c r="AP227" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ227" s="14" t="inlineStr"/>
@@ -32275,9 +32227,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX227" s="17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX227" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -32341,31 +32293,15 @@
       <c r="U228" s="14" t="n">
         <v>2.6</v>
       </c>
-      <c r="V228" s="14" t="n">
-        <v>1.5874</v>
-      </c>
-      <c r="W228" s="14" t="n">
-        <v>1.8764</v>
-      </c>
+      <c r="V228" s="14" t="inlineStr"/>
+      <c r="W228" s="14" t="inlineStr"/>
       <c r="X228" s="14" t="inlineStr"/>
-      <c r="Y228" s="14" t="n">
-        <v>-4.27</v>
-      </c>
-      <c r="Z228" s="14" t="n">
-        <v>-29.45</v>
-      </c>
-      <c r="AA228" s="14" t="n">
-        <v>2.1769</v>
-      </c>
-      <c r="AB228" s="14" t="n">
-        <v>1.3714</v>
-      </c>
-      <c r="AC228" s="14" t="n">
-        <v>1.4155</v>
-      </c>
-      <c r="AD228" s="14" t="n">
-        <v>1.056534588313268</v>
-      </c>
+      <c r="Y228" s="14" t="inlineStr"/>
+      <c r="Z228" s="14" t="inlineStr"/>
+      <c r="AA228" s="14" t="inlineStr"/>
+      <c r="AB228" s="14" t="inlineStr"/>
+      <c r="AC228" s="14" t="inlineStr"/>
+      <c r="AD228" s="14" t="inlineStr"/>
       <c r="AE228" s="14" t="inlineStr"/>
       <c r="AF228" s="14" t="inlineStr"/>
       <c r="AG228" s="14" t="inlineStr"/>
@@ -32403,7 +32339,7 @@
       </c>
       <c r="AP228" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ228" s="14" t="inlineStr"/>
@@ -32495,33 +32431,15 @@
       <c r="U229" s="14" t="n">
         <v>0.88</v>
       </c>
-      <c r="V229" s="14" t="n">
-        <v>1.5693</v>
-      </c>
-      <c r="W229" s="14" t="n">
-        <v>1.7022</v>
-      </c>
-      <c r="X229" s="14" t="n">
-        <v>0.9827</v>
-      </c>
-      <c r="Y229" s="14" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="Z229" s="14" t="n">
-        <v>39.61</v>
-      </c>
-      <c r="AA229" s="14" t="n">
-        <v>2.2068</v>
-      </c>
-      <c r="AB229" s="14" t="n">
-        <v>1.4062</v>
-      </c>
-      <c r="AC229" s="14" t="n">
-        <v>1.4907</v>
-      </c>
-      <c r="AD229" s="14" t="n">
-        <v>1.004899268305929</v>
-      </c>
+      <c r="V229" s="14" t="inlineStr"/>
+      <c r="W229" s="14" t="inlineStr"/>
+      <c r="X229" s="14" t="inlineStr"/>
+      <c r="Y229" s="14" t="inlineStr"/>
+      <c r="Z229" s="14" t="inlineStr"/>
+      <c r="AA229" s="14" t="inlineStr"/>
+      <c r="AB229" s="14" t="inlineStr"/>
+      <c r="AC229" s="14" t="inlineStr"/>
+      <c r="AD229" s="14" t="inlineStr"/>
       <c r="AE229" s="14" t="inlineStr"/>
       <c r="AF229" s="14" t="inlineStr"/>
       <c r="AG229" s="14" t="inlineStr"/>
@@ -32559,7 +32477,7 @@
       </c>
       <c r="AP229" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ229" s="14" t="inlineStr"/>
@@ -32651,33 +32569,15 @@
       <c r="U230" s="14" t="n">
         <v>1.64</v>
       </c>
-      <c r="V230" s="14" t="n">
-        <v>1.4448</v>
-      </c>
-      <c r="W230" s="14" t="n">
-        <v>1.5301</v>
-      </c>
-      <c r="X230" s="14" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="Y230" s="14" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="Z230" s="14" t="n">
-        <v>47.92</v>
-      </c>
-      <c r="AA230" s="14" t="n">
-        <v>2.2684</v>
-      </c>
-      <c r="AB230" s="14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC230" s="14" t="n">
-        <v>1.6469</v>
-      </c>
-      <c r="AD230" s="14" t="n">
-        <v>0.8899116742872167</v>
-      </c>
+      <c r="V230" s="14" t="inlineStr"/>
+      <c r="W230" s="14" t="inlineStr"/>
+      <c r="X230" s="14" t="inlineStr"/>
+      <c r="Y230" s="14" t="inlineStr"/>
+      <c r="Z230" s="14" t="inlineStr"/>
+      <c r="AA230" s="14" t="inlineStr"/>
+      <c r="AB230" s="14" t="inlineStr"/>
+      <c r="AC230" s="14" t="inlineStr"/>
+      <c r="AD230" s="14" t="inlineStr"/>
       <c r="AE230" s="14" t="inlineStr"/>
       <c r="AF230" s="14" t="inlineStr"/>
       <c r="AG230" s="14" t="inlineStr"/>
@@ -32715,7 +32615,7 @@
       </c>
       <c r="AP230" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ230" s="14" t="inlineStr"/>
@@ -32807,33 +32707,15 @@
       <c r="U231" s="14" t="n">
         <v>1.67</v>
       </c>
-      <c r="V231" s="14" t="n">
-        <v>1.2317</v>
-      </c>
-      <c r="W231" s="14" t="n">
-        <v>1.4016</v>
-      </c>
-      <c r="X231" s="14" t="n">
-        <v>1.9597</v>
-      </c>
-      <c r="Y231" s="14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z231" s="14" t="n">
-        <v>30.42</v>
-      </c>
-      <c r="AA231" s="14" t="n">
-        <v>2.2031</v>
-      </c>
-      <c r="AB231" s="14" t="n">
-        <v>1.7886</v>
-      </c>
-      <c r="AC231" s="14" t="n">
-        <v>1.9317</v>
-      </c>
-      <c r="AD231" s="14" t="n">
-        <v>0.9834197397349418</v>
-      </c>
+      <c r="V231" s="14" t="inlineStr"/>
+      <c r="W231" s="14" t="inlineStr"/>
+      <c r="X231" s="14" t="inlineStr"/>
+      <c r="Y231" s="14" t="inlineStr"/>
+      <c r="Z231" s="14" t="inlineStr"/>
+      <c r="AA231" s="14" t="inlineStr"/>
+      <c r="AB231" s="14" t="inlineStr"/>
+      <c r="AC231" s="14" t="inlineStr"/>
+      <c r="AD231" s="14" t="inlineStr"/>
       <c r="AE231" s="14" t="inlineStr"/>
       <c r="AF231" s="14" t="inlineStr"/>
       <c r="AG231" s="14" t="inlineStr"/>
@@ -32871,7 +32753,7 @@
       </c>
       <c r="AP231" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ231" s="14" t="inlineStr"/>
@@ -32963,33 +32845,15 @@
       <c r="U232" s="14" t="n">
         <v>0.85</v>
       </c>
-      <c r="V232" s="14" t="n">
-        <v>1.3869</v>
-      </c>
-      <c r="W232" s="14" t="n">
-        <v>1.3491</v>
-      </c>
-      <c r="X232" s="14" t="n">
-        <v>1.4837</v>
-      </c>
-      <c r="Y232" s="14" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="Z232" s="14" t="n">
-        <v>11.84</v>
-      </c>
-      <c r="AA232" s="14" t="n">
-        <v>2.1812</v>
-      </c>
-      <c r="AB232" s="14" t="n">
-        <v>1.5727</v>
-      </c>
-      <c r="AC232" s="14" t="n">
-        <v>1.5517</v>
-      </c>
-      <c r="AD232" s="14" t="n">
-        <v>1.045761321555791</v>
-      </c>
+      <c r="V232" s="14" t="inlineStr"/>
+      <c r="W232" s="14" t="inlineStr"/>
+      <c r="X232" s="14" t="inlineStr"/>
+      <c r="Y232" s="14" t="inlineStr"/>
+      <c r="Z232" s="14" t="inlineStr"/>
+      <c r="AA232" s="14" t="inlineStr"/>
+      <c r="AB232" s="14" t="inlineStr"/>
+      <c r="AC232" s="14" t="inlineStr"/>
+      <c r="AD232" s="14" t="inlineStr"/>
       <c r="AE232" s="14" t="inlineStr"/>
       <c r="AF232" s="14" t="inlineStr"/>
       <c r="AG232" s="14" t="inlineStr"/>
@@ -33027,7 +32891,7 @@
       </c>
       <c r="AP232" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ232" s="14" t="inlineStr"/>
@@ -33123,33 +32987,15 @@
       <c r="U233" s="14" t="n">
         <v>0.52</v>
       </c>
-      <c r="V233" s="14" t="n">
-        <v>1.2798</v>
-      </c>
-      <c r="W233" s="14" t="n">
-        <v>1.2963</v>
-      </c>
-      <c r="X233" s="14" t="n">
-        <v>1.1789</v>
-      </c>
-      <c r="Y233" s="14" t="n">
-        <v>-7.08</v>
-      </c>
-      <c r="Z233" s="14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA233" s="14" t="n">
-        <v>2.1077</v>
-      </c>
-      <c r="AB233" s="14" t="n">
-        <v>1.6469</v>
-      </c>
-      <c r="AC233" s="14" t="n">
-        <v>1.6688</v>
-      </c>
-      <c r="AD233" s="14" t="n">
-        <v>1.03172931627156</v>
-      </c>
+      <c r="V233" s="14" t="inlineStr"/>
+      <c r="W233" s="14" t="inlineStr"/>
+      <c r="X233" s="14" t="inlineStr"/>
+      <c r="Y233" s="14" t="inlineStr"/>
+      <c r="Z233" s="14" t="inlineStr"/>
+      <c r="AA233" s="14" t="inlineStr"/>
+      <c r="AB233" s="14" t="inlineStr"/>
+      <c r="AC233" s="14" t="inlineStr"/>
+      <c r="AD233" s="14" t="inlineStr"/>
       <c r="AE233" s="14" t="inlineStr"/>
       <c r="AF233" s="14" t="inlineStr"/>
       <c r="AG233" s="14" t="inlineStr"/>
@@ -33187,7 +33033,7 @@
       </c>
       <c r="AP233" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ233" s="14" t="inlineStr"/>
@@ -33217,9 +33063,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX233" s="17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX233" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -33283,33 +33129,15 @@
       <c r="U234" s="14" t="n">
         <v>0.59</v>
       </c>
-      <c r="V234" s="14" t="n">
-        <v>1.2492</v>
-      </c>
-      <c r="W234" s="14" t="n">
-        <v>1.3039</v>
-      </c>
-      <c r="X234" s="14" t="n">
-        <v>1.0848</v>
-      </c>
-      <c r="Y234" s="14" t="n">
-        <v>-5.82</v>
-      </c>
-      <c r="Z234" s="14" t="n">
-        <v>-7.13</v>
-      </c>
-      <c r="AA234" s="14" t="n">
-        <v>2.0749</v>
-      </c>
-      <c r="AB234" s="14" t="n">
-        <v>1.661</v>
-      </c>
-      <c r="AC234" s="14" t="n">
-        <v>1.6171</v>
-      </c>
-      <c r="AD234" s="14" t="n">
-        <v>1.09649748302873</v>
-      </c>
+      <c r="V234" s="14" t="inlineStr"/>
+      <c r="W234" s="14" t="inlineStr"/>
+      <c r="X234" s="14" t="inlineStr"/>
+      <c r="Y234" s="14" t="inlineStr"/>
+      <c r="Z234" s="14" t="inlineStr"/>
+      <c r="AA234" s="14" t="inlineStr"/>
+      <c r="AB234" s="14" t="inlineStr"/>
+      <c r="AC234" s="14" t="inlineStr"/>
+      <c r="AD234" s="14" t="inlineStr"/>
       <c r="AE234" s="14" t="inlineStr"/>
       <c r="AF234" s="14" t="inlineStr"/>
       <c r="AG234" s="14" t="inlineStr"/>
@@ -33347,7 +33175,7 @@
       </c>
       <c r="AP234" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ234" s="14" t="inlineStr"/>
@@ -33439,33 +33267,15 @@
       <c r="U235" s="14" t="n">
         <v>0.32</v>
       </c>
-      <c r="V235" s="14" t="n">
-        <v>1.2842</v>
-      </c>
-      <c r="W235" s="14" t="n">
-        <v>1.2709</v>
-      </c>
-      <c r="X235" s="14" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="Y235" s="14" t="n">
-        <v>-4.35</v>
-      </c>
-      <c r="Z235" s="14" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AA235" s="14" t="n">
-        <v>2.0864</v>
-      </c>
-      <c r="AB235" s="14" t="n">
-        <v>1.6247</v>
-      </c>
-      <c r="AC235" s="14" t="n">
-        <v>1.474</v>
-      </c>
-      <c r="AD235" s="14" t="n">
-        <v>0.9865310322949488</v>
-      </c>
+      <c r="V235" s="14" t="inlineStr"/>
+      <c r="W235" s="14" t="inlineStr"/>
+      <c r="X235" s="14" t="inlineStr"/>
+      <c r="Y235" s="14" t="inlineStr"/>
+      <c r="Z235" s="14" t="inlineStr"/>
+      <c r="AA235" s="14" t="inlineStr"/>
+      <c r="AB235" s="14" t="inlineStr"/>
+      <c r="AC235" s="14" t="inlineStr"/>
+      <c r="AD235" s="14" t="inlineStr"/>
       <c r="AE235" s="14" t="inlineStr"/>
       <c r="AF235" s="14" t="inlineStr"/>
       <c r="AG235" s="14" t="inlineStr"/>
@@ -33503,7 +33313,7 @@
       </c>
       <c r="AP235" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ235" s="14" t="inlineStr"/>
@@ -33595,33 +33405,15 @@
       <c r="U236" s="14" t="n">
         <v>0.21</v>
       </c>
-      <c r="V236" s="14" t="n">
-        <v>1.1976</v>
-      </c>
-      <c r="W236" s="14" t="n">
-        <v>1.2424</v>
-      </c>
-      <c r="X236" s="14" t="n">
-        <v>0.8063</v>
-      </c>
-      <c r="Y236" s="14" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="Z236" s="14" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="AA236" s="14" t="n">
-        <v>2.1227</v>
-      </c>
-      <c r="AB236" s="14" t="n">
-        <v>1.7724</v>
-      </c>
-      <c r="AC236" s="14" t="n">
-        <v>1.5575</v>
-      </c>
-      <c r="AD236" s="14" t="n">
-        <v>0.9246068773433632</v>
-      </c>
+      <c r="V236" s="14" t="inlineStr"/>
+      <c r="W236" s="14" t="inlineStr"/>
+      <c r="X236" s="14" t="inlineStr"/>
+      <c r="Y236" s="14" t="inlineStr"/>
+      <c r="Z236" s="14" t="inlineStr"/>
+      <c r="AA236" s="14" t="inlineStr"/>
+      <c r="AB236" s="14" t="inlineStr"/>
+      <c r="AC236" s="14" t="inlineStr"/>
+      <c r="AD236" s="14" t="inlineStr"/>
       <c r="AE236" s="14" t="inlineStr"/>
       <c r="AF236" s="14" t="inlineStr"/>
       <c r="AG236" s="14" t="inlineStr"/>
@@ -33659,7 +33451,7 @@
       </c>
       <c r="AP236" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ236" s="14" t="inlineStr"/>
@@ -33685,9 +33477,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX236" s="17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX236" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -33751,33 +33543,15 @@
       <c r="U237" s="14" t="n">
         <v>0.3</v>
       </c>
-      <c r="V237" s="14" t="n">
-        <v>1.1501</v>
-      </c>
-      <c r="W237" s="14" t="n">
-        <v>1.2072</v>
-      </c>
-      <c r="X237" s="14" t="n">
-        <v>1.1512</v>
-      </c>
-      <c r="Y237" s="14" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="Z237" s="14" t="n">
-        <v>14.05</v>
-      </c>
-      <c r="AA237" s="14" t="n">
-        <v>2.1788</v>
-      </c>
-      <c r="AB237" s="14" t="n">
-        <v>1.8944</v>
-      </c>
-      <c r="AC237" s="14" t="n">
-        <v>1.7863</v>
-      </c>
-      <c r="AD237" s="14" t="n">
-        <v>0.9820139782817532</v>
-      </c>
+      <c r="V237" s="14" t="inlineStr"/>
+      <c r="W237" s="14" t="inlineStr"/>
+      <c r="X237" s="14" t="inlineStr"/>
+      <c r="Y237" s="14" t="inlineStr"/>
+      <c r="Z237" s="14" t="inlineStr"/>
+      <c r="AA237" s="14" t="inlineStr"/>
+      <c r="AB237" s="14" t="inlineStr"/>
+      <c r="AC237" s="14" t="inlineStr"/>
+      <c r="AD237" s="14" t="inlineStr"/>
       <c r="AE237" s="14" t="inlineStr"/>
       <c r="AF237" s="14" t="inlineStr"/>
       <c r="AG237" s="14" t="inlineStr"/>
@@ -33815,7 +33589,7 @@
       </c>
       <c r="AP237" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ237" s="14" t="inlineStr"/>
@@ -33907,33 +33681,15 @@
       <c r="U238" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="V238" s="14" t="n">
-        <v>1.181</v>
-      </c>
-      <c r="W238" s="14" t="n">
-        <v>1.1757</v>
-      </c>
-      <c r="X238" s="14" t="n">
-        <v>1.0916</v>
-      </c>
-      <c r="Y238" s="14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Z238" s="14" t="n">
-        <v>10.96</v>
-      </c>
-      <c r="AA238" s="14" t="n">
-        <v>2.1289</v>
-      </c>
-      <c r="AB238" s="14" t="n">
-        <v>1.8027</v>
-      </c>
-      <c r="AC238" s="14" t="n">
-        <v>1.8217</v>
-      </c>
-      <c r="AD238" s="14" t="n">
-        <v>1.013262330913718</v>
-      </c>
+      <c r="V238" s="14" t="inlineStr"/>
+      <c r="W238" s="14" t="inlineStr"/>
+      <c r="X238" s="14" t="inlineStr"/>
+      <c r="Y238" s="14" t="inlineStr"/>
+      <c r="Z238" s="14" t="inlineStr"/>
+      <c r="AA238" s="14" t="inlineStr"/>
+      <c r="AB238" s="14" t="inlineStr"/>
+      <c r="AC238" s="14" t="inlineStr"/>
+      <c r="AD238" s="14" t="inlineStr"/>
       <c r="AE238" s="14" t="inlineStr"/>
       <c r="AF238" s="14" t="inlineStr"/>
       <c r="AG238" s="14" t="inlineStr"/>
@@ -33971,7 +33727,7 @@
       </c>
       <c r="AP238" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ238" s="14" t="inlineStr"/>
@@ -34063,33 +33819,15 @@
       <c r="U239" s="14" t="n">
         <v>0.83</v>
       </c>
-      <c r="V239" s="14" t="n">
-        <v>1.142</v>
-      </c>
-      <c r="W239" s="14" t="n">
-        <v>1.1572</v>
-      </c>
-      <c r="X239" s="14" t="n">
-        <v>1.202</v>
-      </c>
-      <c r="Y239" s="14" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="Z239" s="14" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="AA239" s="14" t="n">
-        <v>2.1913</v>
-      </c>
-      <c r="AB239" s="14" t="n">
-        <v>1.9189</v>
-      </c>
-      <c r="AC239" s="14" t="n">
-        <v>1.9438</v>
-      </c>
-      <c r="AD239" s="14" t="n">
-        <v>0.8616386298345911</v>
-      </c>
+      <c r="V239" s="14" t="inlineStr"/>
+      <c r="W239" s="14" t="inlineStr"/>
+      <c r="X239" s="14" t="inlineStr"/>
+      <c r="Y239" s="14" t="inlineStr"/>
+      <c r="Z239" s="14" t="inlineStr"/>
+      <c r="AA239" s="14" t="inlineStr"/>
+      <c r="AB239" s="14" t="inlineStr"/>
+      <c r="AC239" s="14" t="inlineStr"/>
+      <c r="AD239" s="14" t="inlineStr"/>
       <c r="AE239" s="14" t="inlineStr"/>
       <c r="AF239" s="14" t="inlineStr"/>
       <c r="AG239" s="14" t="inlineStr"/>
@@ -34127,7 +33865,7 @@
       </c>
       <c r="AP239" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ239" s="14" t="inlineStr"/>
@@ -34219,33 +33957,15 @@
       <c r="U240" s="14" t="n">
         <v>0.35</v>
       </c>
-      <c r="V240" s="14" t="n">
-        <v>1.094</v>
-      </c>
-      <c r="W240" s="14" t="n">
-        <v>1.1379</v>
-      </c>
-      <c r="X240" s="14" t="n">
-        <v>1.4001</v>
-      </c>
-      <c r="Y240" s="14" t="n">
-        <v>-2.31</v>
-      </c>
-      <c r="Z240" s="14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA240" s="14" t="n">
-        <v>2.1284</v>
-      </c>
-      <c r="AB240" s="14" t="n">
-        <v>1.9455</v>
-      </c>
-      <c r="AC240" s="14" t="n">
-        <v>2.0637</v>
-      </c>
-      <c r="AD240" s="14" t="n">
-        <v>0.8867220447577452</v>
-      </c>
+      <c r="V240" s="14" t="inlineStr"/>
+      <c r="W240" s="14" t="inlineStr"/>
+      <c r="X240" s="14" t="inlineStr"/>
+      <c r="Y240" s="14" t="inlineStr"/>
+      <c r="Z240" s="14" t="inlineStr"/>
+      <c r="AA240" s="14" t="inlineStr"/>
+      <c r="AB240" s="14" t="inlineStr"/>
+      <c r="AC240" s="14" t="inlineStr"/>
+      <c r="AD240" s="14" t="inlineStr"/>
       <c r="AE240" s="14" t="inlineStr"/>
       <c r="AF240" s="14" t="inlineStr"/>
       <c r="AG240" s="14" t="inlineStr"/>
@@ -34283,7 +34003,7 @@
       </c>
       <c r="AP240" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ240" s="14" t="inlineStr"/>
@@ -34309,9 +34029,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX240" s="17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX240" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -34375,33 +34095,15 @@
       <c r="U241" s="14" t="n">
         <v>0.9</v>
       </c>
-      <c r="V241" s="14" t="n">
-        <v>0.9808</v>
-      </c>
-      <c r="W241" s="14" t="n">
-        <v>1.0683</v>
-      </c>
-      <c r="X241" s="14" t="n">
-        <v>1.5024</v>
-      </c>
-      <c r="Y241" s="14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Z241" s="14" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="AA241" s="14" t="n">
-        <v>2.1437</v>
-      </c>
-      <c r="AB241" s="14" t="n">
-        <v>2.1857</v>
-      </c>
-      <c r="AC241" s="14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD241" s="14" t="n">
-        <v>1.023923666006314</v>
-      </c>
+      <c r="V241" s="14" t="inlineStr"/>
+      <c r="W241" s="14" t="inlineStr"/>
+      <c r="X241" s="14" t="inlineStr"/>
+      <c r="Y241" s="14" t="inlineStr"/>
+      <c r="Z241" s="14" t="inlineStr"/>
+      <c r="AA241" s="14" t="inlineStr"/>
+      <c r="AB241" s="14" t="inlineStr"/>
+      <c r="AC241" s="14" t="inlineStr"/>
+      <c r="AD241" s="14" t="inlineStr"/>
       <c r="AE241" s="14" t="inlineStr"/>
       <c r="AF241" s="14" t="inlineStr"/>
       <c r="AG241" s="14" t="inlineStr"/>
@@ -34439,7 +34141,7 @@
       </c>
       <c r="AP241" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ241" s="14" t="inlineStr"/>
@@ -34531,33 +34233,15 @@
       <c r="U242" s="14" t="n">
         <v>0.4</v>
       </c>
-      <c r="V242" s="14" t="n">
-        <v>0.9424</v>
-      </c>
-      <c r="W242" s="14" t="n">
-        <v>1.0018</v>
-      </c>
-      <c r="X242" s="14" t="n">
-        <v>1.3686</v>
-      </c>
-      <c r="Y242" s="14" t="n">
-        <v>-3.47</v>
-      </c>
-      <c r="Z242" s="14" t="n">
-        <v>16.97</v>
-      </c>
-      <c r="AA242" s="14" t="n">
-        <v>2.1152</v>
-      </c>
-      <c r="AB242" s="14" t="n">
-        <v>2.2446</v>
-      </c>
-      <c r="AC242" s="14" t="n">
-        <v>2.4447</v>
-      </c>
-      <c r="AD242" s="14" t="n">
-        <v>0.8652339838692522</v>
-      </c>
+      <c r="V242" s="14" t="inlineStr"/>
+      <c r="W242" s="14" t="inlineStr"/>
+      <c r="X242" s="14" t="inlineStr"/>
+      <c r="Y242" s="14" t="inlineStr"/>
+      <c r="Z242" s="14" t="inlineStr"/>
+      <c r="AA242" s="14" t="inlineStr"/>
+      <c r="AB242" s="14" t="inlineStr"/>
+      <c r="AC242" s="14" t="inlineStr"/>
+      <c r="AD242" s="14" t="inlineStr"/>
       <c r="AE242" s="14" t="inlineStr"/>
       <c r="AF242" s="14" t="inlineStr"/>
       <c r="AG242" s="14" t="inlineStr"/>
@@ -34595,7 +34279,7 @@
       </c>
       <c r="AP242" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ242" s="14" t="inlineStr"/>
@@ -34621,9 +34305,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX242" s="17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX242" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -34687,33 +34371,15 @@
       <c r="U243" s="14" t="n">
         <v>0.43</v>
       </c>
-      <c r="V243" s="14" t="n">
-        <v>0.8564000000000001</v>
-      </c>
-      <c r="W243" s="14" t="n">
-        <v>0.9238</v>
-      </c>
-      <c r="X243" s="14" t="n">
-        <v>1.5108</v>
-      </c>
-      <c r="Y243" s="14" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="Z243" s="14" t="n">
-        <v>26.89</v>
-      </c>
-      <c r="AA243" s="14" t="n">
-        <v>2.1141</v>
-      </c>
-      <c r="AB243" s="14" t="n">
-        <v>2.4686</v>
-      </c>
-      <c r="AC243" s="14" t="n">
-        <v>2.7523</v>
-      </c>
-      <c r="AD243" s="14" t="n">
-        <v>0.8728449222675577</v>
-      </c>
+      <c r="V243" s="14" t="inlineStr"/>
+      <c r="W243" s="14" t="inlineStr"/>
+      <c r="X243" s="14" t="inlineStr"/>
+      <c r="Y243" s="14" t="inlineStr"/>
+      <c r="Z243" s="14" t="inlineStr"/>
+      <c r="AA243" s="14" t="inlineStr"/>
+      <c r="AB243" s="14" t="inlineStr"/>
+      <c r="AC243" s="14" t="inlineStr"/>
+      <c r="AD243" s="14" t="inlineStr"/>
       <c r="AE243" s="14" t="inlineStr"/>
       <c r="AF243" s="14" t="inlineStr"/>
       <c r="AG243" s="14" t="inlineStr"/>
@@ -34751,7 +34417,7 @@
       </c>
       <c r="AP243" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ243" s="14" t="inlineStr"/>
@@ -34843,33 +34509,15 @@
       <c r="U244" s="14" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="V244" s="14" t="n">
-        <v>0.9137999999999999</v>
-      </c>
-      <c r="W244" s="14" t="n">
-        <v>0.9026</v>
-      </c>
-      <c r="X244" s="14" t="n">
-        <v>1.2595</v>
-      </c>
-      <c r="Y244" s="14" t="n">
-        <v>-4.41</v>
-      </c>
-      <c r="Z244" s="14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA244" s="14" t="n">
-        <v>2.0492</v>
-      </c>
-      <c r="AB244" s="14" t="n">
-        <v>2.2425</v>
-      </c>
-      <c r="AC244" s="14" t="n">
-        <v>2.4483</v>
-      </c>
-      <c r="AD244" s="14" t="n">
-        <v>1.023775102281353</v>
-      </c>
+      <c r="V244" s="14" t="inlineStr"/>
+      <c r="W244" s="14" t="inlineStr"/>
+      <c r="X244" s="14" t="inlineStr"/>
+      <c r="Y244" s="14" t="inlineStr"/>
+      <c r="Z244" s="14" t="inlineStr"/>
+      <c r="AA244" s="14" t="inlineStr"/>
+      <c r="AB244" s="14" t="inlineStr"/>
+      <c r="AC244" s="14" t="inlineStr"/>
+      <c r="AD244" s="14" t="inlineStr"/>
       <c r="AE244" s="14" t="inlineStr"/>
       <c r="AF244" s="14" t="inlineStr"/>
       <c r="AG244" s="14" t="inlineStr"/>
@@ -34907,7 +34555,7 @@
       </c>
       <c r="AP244" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ244" s="14" t="inlineStr"/>
@@ -35003,33 +34651,15 @@
       <c r="U245" s="14" t="n">
         <v>0.73</v>
       </c>
-      <c r="V245" s="14" t="n">
-        <v>0.9123</v>
-      </c>
-      <c r="W245" s="14" t="n">
-        <v>0.8928</v>
-      </c>
-      <c r="X245" s="14" t="n">
-        <v>1.1486</v>
-      </c>
-      <c r="Y245" s="14" t="n">
-        <v>-5.03</v>
-      </c>
-      <c r="Z245" s="14" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="AA245" s="14" t="n">
-        <v>2.0089</v>
-      </c>
-      <c r="AB245" s="14" t="n">
-        <v>2.202</v>
-      </c>
-      <c r="AC245" s="14" t="n">
-        <v>2.3704</v>
-      </c>
-      <c r="AD245" s="14" t="n">
-        <v>0.956610269871034</v>
-      </c>
+      <c r="V245" s="14" t="inlineStr"/>
+      <c r="W245" s="14" t="inlineStr"/>
+      <c r="X245" s="14" t="inlineStr"/>
+      <c r="Y245" s="14" t="inlineStr"/>
+      <c r="Z245" s="14" t="inlineStr"/>
+      <c r="AA245" s="14" t="inlineStr"/>
+      <c r="AB245" s="14" t="inlineStr"/>
+      <c r="AC245" s="14" t="inlineStr"/>
+      <c r="AD245" s="14" t="inlineStr"/>
       <c r="AE245" s="14" t="inlineStr"/>
       <c r="AF245" s="14" t="inlineStr"/>
       <c r="AG245" s="14" t="inlineStr"/>
@@ -35067,7 +34697,7 @@
       </c>
       <c r="AP245" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ245" s="14" t="inlineStr"/>
@@ -35159,33 +34789,15 @@
       <c r="U246" s="14" t="n">
         <v>0.91</v>
       </c>
-      <c r="V246" s="14" t="n">
-        <v>0.9659</v>
-      </c>
-      <c r="W246" s="14" t="n">
-        <v>0.9298999999999999</v>
-      </c>
-      <c r="X246" s="14" t="n">
-        <v>0.9817</v>
-      </c>
-      <c r="Y246" s="14" t="n">
-        <v>-4.93</v>
-      </c>
-      <c r="Z246" s="14" t="n">
-        <v>-15.71</v>
-      </c>
-      <c r="AA246" s="14" t="n">
-        <v>2.0098</v>
-      </c>
-      <c r="AB246" s="14" t="n">
-        <v>2.0807</v>
-      </c>
-      <c r="AC246" s="14" t="n">
-        <v>2.2971</v>
-      </c>
-      <c r="AD246" s="14" t="n">
-        <v>1.030650727232781</v>
-      </c>
+      <c r="V246" s="14" t="inlineStr"/>
+      <c r="W246" s="14" t="inlineStr"/>
+      <c r="X246" s="14" t="inlineStr"/>
+      <c r="Y246" s="14" t="inlineStr"/>
+      <c r="Z246" s="14" t="inlineStr"/>
+      <c r="AA246" s="14" t="inlineStr"/>
+      <c r="AB246" s="14" t="inlineStr"/>
+      <c r="AC246" s="14" t="inlineStr"/>
+      <c r="AD246" s="14" t="inlineStr"/>
       <c r="AE246" s="14" t="inlineStr"/>
       <c r="AF246" s="14" t="inlineStr"/>
       <c r="AG246" s="14" t="inlineStr"/>
@@ -35223,7 +34835,7 @@
       </c>
       <c r="AP246" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ246" s="14" t="inlineStr"/>
@@ -35319,33 +34931,15 @@
       <c r="U247" s="14" t="n">
         <v>0.97</v>
       </c>
-      <c r="V247" s="14" t="n">
-        <v>0.9155</v>
-      </c>
-      <c r="W247" s="14" t="n">
-        <v>0.9306</v>
-      </c>
-      <c r="X247" s="14" t="n">
-        <v>1.0524</v>
-      </c>
-      <c r="Y247" s="14" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="Z247" s="14" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="AA247" s="14" t="n">
-        <v>2.033</v>
-      </c>
-      <c r="AB247" s="14" t="n">
-        <v>2.2206</v>
-      </c>
-      <c r="AC247" s="14" t="n">
-        <v>2.5727</v>
-      </c>
-      <c r="AD247" s="14" t="n">
-        <v>1.060730772792007</v>
-      </c>
+      <c r="V247" s="14" t="inlineStr"/>
+      <c r="W247" s="14" t="inlineStr"/>
+      <c r="X247" s="14" t="inlineStr"/>
+      <c r="Y247" s="14" t="inlineStr"/>
+      <c r="Z247" s="14" t="inlineStr"/>
+      <c r="AA247" s="14" t="inlineStr"/>
+      <c r="AB247" s="14" t="inlineStr"/>
+      <c r="AC247" s="14" t="inlineStr"/>
+      <c r="AD247" s="14" t="inlineStr"/>
       <c r="AE247" s="14" t="inlineStr"/>
       <c r="AF247" s="14" t="inlineStr"/>
       <c r="AG247" s="14" t="inlineStr"/>
@@ -35383,7 +34977,7 @@
       </c>
       <c r="AP247" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ247" s="14" t="inlineStr"/>
@@ -35475,33 +35069,15 @@
       <c r="U248" s="14" t="n">
         <v>1.45</v>
       </c>
-      <c r="V248" s="14" t="n">
-        <v>0.8895999999999999</v>
-      </c>
-      <c r="W248" s="14" t="n">
-        <v>0.9227</v>
-      </c>
-      <c r="X248" s="14" t="n">
-        <v>0.9617</v>
-      </c>
-      <c r="Y248" s="14" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="Z248" s="14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AA248" s="14" t="n">
-        <v>1.9978</v>
-      </c>
-      <c r="AB248" s="14" t="n">
-        <v>2.2457</v>
-      </c>
-      <c r="AC248" s="14" t="n">
-        <v>2.647</v>
-      </c>
-      <c r="AD248" s="14" t="n">
-        <v>1.005539892241721</v>
-      </c>
+      <c r="V248" s="14" t="inlineStr"/>
+      <c r="W248" s="14" t="inlineStr"/>
+      <c r="X248" s="14" t="inlineStr"/>
+      <c r="Y248" s="14" t="inlineStr"/>
+      <c r="Z248" s="14" t="inlineStr"/>
+      <c r="AA248" s="14" t="inlineStr"/>
+      <c r="AB248" s="14" t="inlineStr"/>
+      <c r="AC248" s="14" t="inlineStr"/>
+      <c r="AD248" s="14" t="inlineStr"/>
       <c r="AE248" s="14" t="inlineStr"/>
       <c r="AF248" s="14" t="inlineStr"/>
       <c r="AG248" s="14" t="inlineStr"/>
@@ -35539,7 +35115,7 @@
       </c>
       <c r="AP248" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ248" s="14" t="inlineStr"/>
@@ -35631,33 +35207,15 @@
       <c r="U249" s="14" t="n">
         <v>1.69</v>
       </c>
-      <c r="V249" s="14" t="n">
-        <v>0.8277</v>
-      </c>
-      <c r="W249" s="14" t="n">
-        <v>0.8766</v>
-      </c>
-      <c r="X249" s="14" t="n">
-        <v>1.1446</v>
-      </c>
-      <c r="Y249" s="14" t="n">
-        <v>-2.38</v>
-      </c>
-      <c r="Z249" s="14" t="n">
-        <v>13.92</v>
-      </c>
-      <c r="AA249" s="14" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="AB249" s="14" t="n">
-        <v>2.3704</v>
-      </c>
-      <c r="AC249" s="14" t="n">
-        <v>2.8023</v>
-      </c>
-      <c r="AD249" s="14" t="n">
-        <v>0.9930318294824144</v>
-      </c>
+      <c r="V249" s="14" t="inlineStr"/>
+      <c r="W249" s="14" t="inlineStr"/>
+      <c r="X249" s="14" t="inlineStr"/>
+      <c r="Y249" s="14" t="inlineStr"/>
+      <c r="Z249" s="14" t="inlineStr"/>
+      <c r="AA249" s="14" t="inlineStr"/>
+      <c r="AB249" s="14" t="inlineStr"/>
+      <c r="AC249" s="14" t="inlineStr"/>
+      <c r="AD249" s="14" t="inlineStr"/>
       <c r="AE249" s="14" t="inlineStr"/>
       <c r="AF249" s="14" t="inlineStr"/>
       <c r="AG249" s="14" t="inlineStr"/>
@@ -35695,7 +35253,7 @@
       </c>
       <c r="AP249" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ249" s="14" t="inlineStr"/>
@@ -35721,9 +35279,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX249" s="17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX249" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -35787,33 +35345,15 @@
       <c r="U250" s="14" t="n">
         <v>1.14</v>
       </c>
-      <c r="V250" s="14" t="n">
-        <v>0.8299</v>
-      </c>
-      <c r="W250" s="14" t="n">
-        <v>0.8485</v>
-      </c>
-      <c r="X250" s="14" t="n">
-        <v>1.1617</v>
-      </c>
-      <c r="Y250" s="14" t="n">
-        <v>-5.33</v>
-      </c>
-      <c r="Z250" s="14" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="AA250" s="14" t="n">
-        <v>1.9246</v>
-      </c>
-      <c r="AB250" s="14" t="n">
-        <v>2.319</v>
-      </c>
-      <c r="AC250" s="14" t="n">
-        <v>2.7538</v>
-      </c>
-      <c r="AD250" s="14" t="n">
-        <v>0.9266762222869668</v>
-      </c>
+      <c r="V250" s="14" t="inlineStr"/>
+      <c r="W250" s="14" t="inlineStr"/>
+      <c r="X250" s="14" t="inlineStr"/>
+      <c r="Y250" s="14" t="inlineStr"/>
+      <c r="Z250" s="14" t="inlineStr"/>
+      <c r="AA250" s="14" t="inlineStr"/>
+      <c r="AB250" s="14" t="inlineStr"/>
+      <c r="AC250" s="14" t="inlineStr"/>
+      <c r="AD250" s="14" t="inlineStr"/>
       <c r="AE250" s="14" t="inlineStr"/>
       <c r="AF250" s="14" t="inlineStr"/>
       <c r="AG250" s="14" t="inlineStr"/>
@@ -35851,7 +35391,7 @@
       </c>
       <c r="AP250" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ250" s="14" t="inlineStr"/>
@@ -35943,33 +35483,15 @@
       <c r="U251" s="14" t="n">
         <v>0.62</v>
       </c>
-      <c r="V251" s="14" t="n">
-        <v>0.8158</v>
-      </c>
-      <c r="W251" s="14" t="n">
-        <v>0.8244</v>
-      </c>
-      <c r="X251" s="14" t="n">
-        <v>1.1969</v>
-      </c>
-      <c r="Y251" s="14" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="Z251" s="14" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AA251" s="14" t="n">
-        <v>1.9208</v>
-      </c>
-      <c r="AB251" s="14" t="n">
-        <v>2.3546</v>
-      </c>
-      <c r="AC251" s="14" t="n">
-        <v>2.7495</v>
-      </c>
-      <c r="AD251" s="14" t="n">
-        <v>0.8825536687874085</v>
-      </c>
+      <c r="V251" s="14" t="inlineStr"/>
+      <c r="W251" s="14" t="inlineStr"/>
+      <c r="X251" s="14" t="inlineStr"/>
+      <c r="Y251" s="14" t="inlineStr"/>
+      <c r="Z251" s="14" t="inlineStr"/>
+      <c r="AA251" s="14" t="inlineStr"/>
+      <c r="AB251" s="14" t="inlineStr"/>
+      <c r="AC251" s="14" t="inlineStr"/>
+      <c r="AD251" s="14" t="inlineStr"/>
       <c r="AE251" s="14" t="inlineStr"/>
       <c r="AF251" s="14" t="inlineStr"/>
       <c r="AG251" s="14" t="inlineStr"/>
@@ -36007,7 +35529,7 @@
       </c>
       <c r="AP251" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ251" s="14" t="inlineStr"/>
@@ -36099,33 +35621,15 @@
       <c r="U252" s="14" t="n">
         <v>1.87</v>
       </c>
-      <c r="V252" s="14" t="n">
-        <v>0.8721</v>
-      </c>
-      <c r="W252" s="14" t="n">
-        <v>0.8387</v>
-      </c>
-      <c r="X252" s="14" t="n">
-        <v>1.0483</v>
-      </c>
-      <c r="Y252" s="14" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="Z252" s="14" t="n">
-        <v>-6.45</v>
-      </c>
-      <c r="AA252" s="14" t="n">
-        <v>1.9339</v>
-      </c>
-      <c r="AB252" s="14" t="n">
-        <v>2.2175</v>
-      </c>
-      <c r="AC252" s="14" t="n">
-        <v>2.6969</v>
-      </c>
-      <c r="AD252" s="14" t="n">
-        <v>0.8325506780508251</v>
-      </c>
+      <c r="V252" s="14" t="inlineStr"/>
+      <c r="W252" s="14" t="inlineStr"/>
+      <c r="X252" s="14" t="inlineStr"/>
+      <c r="Y252" s="14" t="inlineStr"/>
+      <c r="Z252" s="14" t="inlineStr"/>
+      <c r="AA252" s="14" t="inlineStr"/>
+      <c r="AB252" s="14" t="inlineStr"/>
+      <c r="AC252" s="14" t="inlineStr"/>
+      <c r="AD252" s="14" t="inlineStr"/>
       <c r="AE252" s="14" t="inlineStr"/>
       <c r="AF252" s="14" t="inlineStr"/>
       <c r="AG252" s="14" t="inlineStr"/>
@@ -36163,7 +35667,7 @@
       </c>
       <c r="AP252" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ252" s="14" t="inlineStr"/>
@@ -36255,33 +35759,15 @@
       <c r="U253" s="14" t="n">
         <v>4.5</v>
       </c>
-      <c r="V253" s="14" t="n">
-        <v>0.7769</v>
-      </c>
-      <c r="W253" s="14" t="n">
-        <v>0.8195</v>
-      </c>
-      <c r="X253" s="14" t="n">
-        <v>1.137</v>
-      </c>
-      <c r="Y253" s="14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z253" s="14" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="AA253" s="14" t="n">
-        <v>1.9625</v>
-      </c>
-      <c r="AB253" s="14" t="n">
-        <v>2.5261</v>
-      </c>
-      <c r="AC253" s="14" t="n">
-        <v>3.0096</v>
-      </c>
-      <c r="AD253" s="14" t="n">
-        <v>0.9418477009824724</v>
-      </c>
+      <c r="V253" s="14" t="inlineStr"/>
+      <c r="W253" s="14" t="inlineStr"/>
+      <c r="X253" s="14" t="inlineStr"/>
+      <c r="Y253" s="14" t="inlineStr"/>
+      <c r="Z253" s="14" t="inlineStr"/>
+      <c r="AA253" s="14" t="inlineStr"/>
+      <c r="AB253" s="14" t="inlineStr"/>
+      <c r="AC253" s="14" t="inlineStr"/>
+      <c r="AD253" s="14" t="inlineStr"/>
       <c r="AE253" s="14" t="inlineStr"/>
       <c r="AF253" s="14" t="inlineStr"/>
       <c r="AG253" s="14" t="inlineStr"/>
@@ -36319,7 +35805,7 @@
       </c>
       <c r="AP253" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ253" s="14" t="inlineStr"/>
@@ -36411,33 +35897,15 @@
       <c r="U254" s="14" t="n">
         <v>3.15</v>
       </c>
-      <c r="V254" s="14" t="n">
-        <v>0.9587</v>
-      </c>
-      <c r="W254" s="14" t="n">
-        <v>0.8625</v>
-      </c>
-      <c r="X254" s="14" t="n">
-        <v>0.7653</v>
-      </c>
-      <c r="Y254" s="14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z254" s="14" t="n">
-        <v>-13.85</v>
-      </c>
-      <c r="AA254" s="14" t="n">
-        <v>1.9447</v>
-      </c>
-      <c r="AB254" s="14" t="n">
-        <v>2.0285</v>
-      </c>
-      <c r="AC254" s="14" t="n">
-        <v>2.1447</v>
-      </c>
-      <c r="AD254" s="14" t="n">
-        <v>0.9496550973326324</v>
-      </c>
+      <c r="V254" s="14" t="inlineStr"/>
+      <c r="W254" s="14" t="inlineStr"/>
+      <c r="X254" s="14" t="inlineStr"/>
+      <c r="Y254" s="14" t="inlineStr"/>
+      <c r="Z254" s="14" t="inlineStr"/>
+      <c r="AA254" s="14" t="inlineStr"/>
+      <c r="AB254" s="14" t="inlineStr"/>
+      <c r="AC254" s="14" t="inlineStr"/>
+      <c r="AD254" s="14" t="inlineStr"/>
       <c r="AE254" s="14" t="n">
         <v>120860.37</v>
       </c>
@@ -36477,7 +35945,7 @@
       </c>
       <c r="AP254" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ254" s="14" t="inlineStr"/>
@@ -36569,33 +36037,15 @@
       <c r="U255" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="V255" s="14" t="n">
-        <v>0.8629</v>
-      </c>
-      <c r="W255" s="14" t="n">
-        <v>0.8596</v>
-      </c>
-      <c r="X255" s="14" t="n">
-        <v>0.8252</v>
-      </c>
-      <c r="Y255" s="14" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="Z255" s="14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA255" s="14" t="n">
-        <v>1.9963</v>
-      </c>
-      <c r="AB255" s="14" t="n">
-        <v>2.3135</v>
-      </c>
-      <c r="AC255" s="14" t="n">
-        <v>2.2723</v>
-      </c>
-      <c r="AD255" s="14" t="n">
-        <v>0.8142457120034781</v>
-      </c>
+      <c r="V255" s="14" t="inlineStr"/>
+      <c r="W255" s="14" t="inlineStr"/>
+      <c r="X255" s="14" t="inlineStr"/>
+      <c r="Y255" s="14" t="inlineStr"/>
+      <c r="Z255" s="14" t="inlineStr"/>
+      <c r="AA255" s="14" t="inlineStr"/>
+      <c r="AB255" s="14" t="inlineStr"/>
+      <c r="AC255" s="14" t="inlineStr"/>
+      <c r="AD255" s="14" t="inlineStr"/>
       <c r="AE255" s="14" t="n">
         <v>98680.88</v>
       </c>
@@ -36635,7 +36085,7 @@
       </c>
       <c r="AP255" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ255" s="14" t="inlineStr"/>
@@ -36661,9 +36111,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX255" s="17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX255" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -36727,33 +36177,15 @@
       <c r="U256" s="14" t="n">
         <v>1.08</v>
       </c>
-      <c r="V256" s="14" t="n">
-        <v>1.0292</v>
-      </c>
-      <c r="W256" s="14" t="n">
-        <v>0.9452</v>
-      </c>
-      <c r="X256" s="14" t="n">
-        <v>0.7513</v>
-      </c>
-      <c r="Y256" s="14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z256" s="14" t="n">
-        <v>-23.26</v>
-      </c>
-      <c r="AA256" s="14" t="n">
-        <v>1.9953</v>
-      </c>
-      <c r="AB256" s="14" t="n">
-        <v>1.9386</v>
-      </c>
-      <c r="AC256" s="14" t="n">
-        <v>2.0656</v>
-      </c>
-      <c r="AD256" s="14" t="n">
-        <v>0.9584829397650404</v>
-      </c>
+      <c r="V256" s="14" t="inlineStr"/>
+      <c r="W256" s="14" t="inlineStr"/>
+      <c r="X256" s="14" t="inlineStr"/>
+      <c r="Y256" s="14" t="inlineStr"/>
+      <c r="Z256" s="14" t="inlineStr"/>
+      <c r="AA256" s="14" t="inlineStr"/>
+      <c r="AB256" s="14" t="inlineStr"/>
+      <c r="AC256" s="14" t="inlineStr"/>
+      <c r="AD256" s="14" t="inlineStr"/>
       <c r="AE256" s="14" t="n">
         <v>43791.69</v>
       </c>
@@ -36793,7 +36225,7 @@
       </c>
       <c r="AP256" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ256" s="14" t="inlineStr"/>
@@ -36885,33 +36317,15 @@
       <c r="U257" s="14" t="n">
         <v>0.82</v>
       </c>
-      <c r="V257" s="14" t="n">
-        <v>1.0712</v>
-      </c>
-      <c r="W257" s="14" t="n">
-        <v>0.9792</v>
-      </c>
-      <c r="X257" s="14" t="n">
-        <v>0.7573</v>
-      </c>
-      <c r="Y257" s="14" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Z257" s="14" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="AA257" s="14" t="n">
-        <v>2.0035</v>
-      </c>
-      <c r="AB257" s="14" t="n">
-        <v>1.8703</v>
-      </c>
-      <c r="AC257" s="14" t="n">
-        <v>2.0423</v>
-      </c>
-      <c r="AD257" s="14" t="n">
-        <v>0.8590722824294629</v>
-      </c>
+      <c r="V257" s="14" t="inlineStr"/>
+      <c r="W257" s="14" t="inlineStr"/>
+      <c r="X257" s="14" t="inlineStr"/>
+      <c r="Y257" s="14" t="inlineStr"/>
+      <c r="Z257" s="14" t="inlineStr"/>
+      <c r="AA257" s="14" t="inlineStr"/>
+      <c r="AB257" s="14" t="inlineStr"/>
+      <c r="AC257" s="14" t="inlineStr"/>
+      <c r="AD257" s="14" t="inlineStr"/>
       <c r="AE257" s="14" t="n">
         <v>20825.05</v>
       </c>
@@ -36951,7 +36365,7 @@
       </c>
       <c r="AP257" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ257" s="14" t="inlineStr"/>
@@ -37043,33 +36457,15 @@
       <c r="U258" s="14" t="n">
         <v>0.48</v>
       </c>
-      <c r="V258" s="14" t="n">
-        <v>1.0242</v>
-      </c>
-      <c r="W258" s="14" t="n">
-        <v>1.0412</v>
-      </c>
-      <c r="X258" s="14" t="n">
-        <v>0.7074</v>
-      </c>
-      <c r="Y258" s="14" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="Z258" s="14" t="n">
-        <v>-15.87</v>
-      </c>
-      <c r="AA258" s="14" t="n">
-        <v>1.9936</v>
-      </c>
-      <c r="AB258" s="14" t="n">
-        <v>1.9464</v>
-      </c>
-      <c r="AC258" s="14" t="n">
-        <v>2.1289</v>
-      </c>
-      <c r="AD258" s="14" t="n">
-        <v>1.07634354892753</v>
-      </c>
+      <c r="V258" s="14" t="inlineStr"/>
+      <c r="W258" s="14" t="inlineStr"/>
+      <c r="X258" s="14" t="inlineStr"/>
+      <c r="Y258" s="14" t="inlineStr"/>
+      <c r="Z258" s="14" t="inlineStr"/>
+      <c r="AA258" s="14" t="inlineStr"/>
+      <c r="AB258" s="14" t="inlineStr"/>
+      <c r="AC258" s="14" t="inlineStr"/>
+      <c r="AD258" s="14" t="inlineStr"/>
       <c r="AE258" s="14" t="n">
         <v>72029.92</v>
       </c>
@@ -37109,7 +36505,7 @@
       </c>
       <c r="AP258" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ258" s="14" t="inlineStr"/>
@@ -37205,33 +36601,15 @@
       <c r="U259" s="14" t="n">
         <v>1.02</v>
       </c>
-      <c r="V259" s="14" t="n">
-        <v>0.9026</v>
-      </c>
-      <c r="W259" s="14" t="n">
-        <v>0.9944</v>
-      </c>
-      <c r="X259" s="14" t="n">
-        <v>1.1449</v>
-      </c>
-      <c r="Y259" s="14" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="Z259" s="14" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="AA259" s="14" t="n">
-        <v>1.9849</v>
-      </c>
-      <c r="AB259" s="14" t="n">
-        <v>2.199</v>
-      </c>
-      <c r="AC259" s="14" t="n">
-        <v>2.4554</v>
-      </c>
-      <c r="AD259" s="14" t="n">
-        <v>0.9344021074234776</v>
-      </c>
+      <c r="V259" s="14" t="inlineStr"/>
+      <c r="W259" s="14" t="inlineStr"/>
+      <c r="X259" s="14" t="inlineStr"/>
+      <c r="Y259" s="14" t="inlineStr"/>
+      <c r="Z259" s="14" t="inlineStr"/>
+      <c r="AA259" s="14" t="inlineStr"/>
+      <c r="AB259" s="14" t="inlineStr"/>
+      <c r="AC259" s="14" t="inlineStr"/>
+      <c r="AD259" s="14" t="inlineStr"/>
       <c r="AE259" s="14" t="n">
         <v>46588.05</v>
       </c>
@@ -37271,7 +36649,7 @@
       </c>
       <c r="AP259" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ259" s="14" t="inlineStr"/>
@@ -37297,9 +36675,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX259" s="17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX259" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -37363,33 +36741,15 @@
       <c r="U260" s="14" t="n">
         <v>1.15</v>
       </c>
-      <c r="V260" s="14" t="n">
-        <v>0.8778</v>
-      </c>
-      <c r="W260" s="14" t="n">
-        <v>0.9308999999999999</v>
-      </c>
-      <c r="X260" s="14" t="n">
-        <v>1.0235</v>
-      </c>
-      <c r="Y260" s="14" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="Z260" s="14" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="AA260" s="14" t="n">
-        <v>1.9712</v>
-      </c>
-      <c r="AB260" s="14" t="n">
-        <v>2.2457</v>
-      </c>
-      <c r="AC260" s="14" t="n">
-        <v>2.3256</v>
-      </c>
-      <c r="AD260" s="14" t="n">
-        <v>0.9753367267882268</v>
-      </c>
+      <c r="V260" s="14" t="inlineStr"/>
+      <c r="W260" s="14" t="inlineStr"/>
+      <c r="X260" s="14" t="inlineStr"/>
+      <c r="Y260" s="14" t="inlineStr"/>
+      <c r="Z260" s="14" t="inlineStr"/>
+      <c r="AA260" s="14" t="inlineStr"/>
+      <c r="AB260" s="14" t="inlineStr"/>
+      <c r="AC260" s="14" t="inlineStr"/>
+      <c r="AD260" s="14" t="inlineStr"/>
       <c r="AE260" s="14" t="n">
         <v>36660.16</v>
       </c>
@@ -37429,7 +36789,7 @@
       </c>
       <c r="AP260" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ260" s="14" t="inlineStr"/>
@@ -37521,33 +36881,15 @@
       <c r="U261" s="14" t="n">
         <v>0.86</v>
       </c>
-      <c r="V261" s="14" t="n">
-        <v>1.0902</v>
-      </c>
-      <c r="W261" s="14" t="n">
-        <v>0.9476</v>
-      </c>
-      <c r="X261" s="14" t="n">
-        <v>0.9423</v>
-      </c>
-      <c r="Y261" s="14" t="n">
-        <v>-1.98</v>
-      </c>
-      <c r="Z261" s="14" t="n">
-        <v>-7.91</v>
-      </c>
-      <c r="AA261" s="14" t="n">
-        <v>1.9542</v>
-      </c>
-      <c r="AB261" s="14" t="n">
-        <v>1.7925</v>
-      </c>
-      <c r="AC261" s="14" t="n">
-        <v>1.9464</v>
-      </c>
-      <c r="AD261" s="14" t="n">
-        <v>0.949664800041624</v>
-      </c>
+      <c r="V261" s="14" t="inlineStr"/>
+      <c r="W261" s="14" t="inlineStr"/>
+      <c r="X261" s="14" t="inlineStr"/>
+      <c r="Y261" s="14" t="inlineStr"/>
+      <c r="Z261" s="14" t="inlineStr"/>
+      <c r="AA261" s="14" t="inlineStr"/>
+      <c r="AB261" s="14" t="inlineStr"/>
+      <c r="AC261" s="14" t="inlineStr"/>
+      <c r="AD261" s="14" t="inlineStr"/>
       <c r="AE261" s="14" t="n">
         <v>42527.9</v>
       </c>
@@ -37587,7 +36929,7 @@
       </c>
       <c r="AP261" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ261" s="14" t="inlineStr"/>
@@ -37679,33 +37021,15 @@
       <c r="U262" s="14" t="n">
         <v>0.52</v>
       </c>
-      <c r="V262" s="14" t="n">
-        <v>1.109</v>
-      </c>
-      <c r="W262" s="14" t="n">
-        <v>1.0136</v>
-      </c>
-      <c r="X262" s="14" t="n">
-        <v>0.962</v>
-      </c>
-      <c r="Y262" s="14" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="Z262" s="14" t="n">
-        <v>-20.2</v>
-      </c>
-      <c r="AA262" s="14" t="n">
-        <v>1.9461</v>
-      </c>
-      <c r="AB262" s="14" t="n">
-        <v>1.7548</v>
-      </c>
-      <c r="AC262" s="14" t="n">
-        <v>1.9647</v>
-      </c>
-      <c r="AD262" s="14" t="n">
-        <v>0.8166694113025433</v>
-      </c>
+      <c r="V262" s="14" t="inlineStr"/>
+      <c r="W262" s="14" t="inlineStr"/>
+      <c r="X262" s="14" t="inlineStr"/>
+      <c r="Y262" s="14" t="inlineStr"/>
+      <c r="Z262" s="14" t="inlineStr"/>
+      <c r="AA262" s="14" t="inlineStr"/>
+      <c r="AB262" s="14" t="inlineStr"/>
+      <c r="AC262" s="14" t="inlineStr"/>
+      <c r="AD262" s="14" t="inlineStr"/>
       <c r="AE262" s="14" t="n">
         <v>18799.51</v>
       </c>
@@ -37745,7 +37069,7 @@
       </c>
       <c r="AP262" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ262" s="14" t="inlineStr"/>
@@ -37837,33 +37161,15 @@
       <c r="U263" s="14" t="n">
         <v>1.13</v>
       </c>
-      <c r="V263" s="14" t="n">
-        <v>1.1565</v>
-      </c>
-      <c r="W263" s="14" t="n">
-        <v>1.1178</v>
-      </c>
-      <c r="X263" s="14" t="n">
-        <v>0.8632</v>
-      </c>
-      <c r="Y263" s="14" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="Z263" s="14" t="n">
-        <v>-25.5</v>
-      </c>
-      <c r="AA263" s="14" t="n">
-        <v>1.9349</v>
-      </c>
-      <c r="AB263" s="14" t="n">
-        <v>1.6731</v>
-      </c>
-      <c r="AC263" s="14" t="n">
-        <v>1.8377</v>
-      </c>
-      <c r="AD263" s="14" t="n">
-        <v>1.059999680578949</v>
-      </c>
+      <c r="V263" s="14" t="inlineStr"/>
+      <c r="W263" s="14" t="inlineStr"/>
+      <c r="X263" s="14" t="inlineStr"/>
+      <c r="Y263" s="14" t="inlineStr"/>
+      <c r="Z263" s="14" t="inlineStr"/>
+      <c r="AA263" s="14" t="inlineStr"/>
+      <c r="AB263" s="14" t="inlineStr"/>
+      <c r="AC263" s="14" t="inlineStr"/>
+      <c r="AD263" s="14" t="inlineStr"/>
       <c r="AE263" s="14" t="n">
         <v>17036.21</v>
       </c>
@@ -37903,7 +37209,7 @@
       </c>
       <c r="AP263" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ263" s="14" t="inlineStr"/>
@@ -37995,33 +37301,15 @@
       <c r="U264" s="14" t="n">
         <v>2.05</v>
       </c>
-      <c r="V264" s="14" t="n">
-        <v>1.3008</v>
-      </c>
-      <c r="W264" s="14" t="n">
-        <v>1.1824</v>
-      </c>
-      <c r="X264" s="14" t="n">
-        <v>0.6421</v>
-      </c>
-      <c r="Y264" s="14" t="n">
-        <v>-3.14</v>
-      </c>
-      <c r="Z264" s="14" t="n">
-        <v>-18.82</v>
-      </c>
-      <c r="AA264" s="14" t="n">
-        <v>1.8929</v>
-      </c>
-      <c r="AB264" s="14" t="n">
-        <v>1.4552</v>
-      </c>
-      <c r="AC264" s="14" t="n">
-        <v>1.5767</v>
-      </c>
-      <c r="AD264" s="14" t="n">
-        <v>0.9419084735050482</v>
-      </c>
+      <c r="V264" s="14" t="inlineStr"/>
+      <c r="W264" s="14" t="inlineStr"/>
+      <c r="X264" s="14" t="inlineStr"/>
+      <c r="Y264" s="14" t="inlineStr"/>
+      <c r="Z264" s="14" t="inlineStr"/>
+      <c r="AA264" s="14" t="inlineStr"/>
+      <c r="AB264" s="14" t="inlineStr"/>
+      <c r="AC264" s="14" t="inlineStr"/>
+      <c r="AD264" s="14" t="inlineStr"/>
       <c r="AE264" s="14" t="n">
         <v>61301.97</v>
       </c>
@@ -38061,7 +37349,7 @@
       </c>
       <c r="AP264" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ264" s="14" t="inlineStr"/>
@@ -38132,12 +37420,8 @@
       <c r="L265" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M265" s="14" t="n">
-        <v>9494889.2988424</v>
-      </c>
-      <c r="N265" s="14" t="n">
-        <v>43608088</v>
-      </c>
+      <c r="M265" s="14" t="inlineStr"/>
+      <c r="N265" s="14" t="inlineStr"/>
       <c r="O265" s="14" t="b">
         <v>1</v>
       </c>
@@ -38157,40 +37441,20 @@
       <c r="U265" s="14" t="n">
         <v>1.49</v>
       </c>
-      <c r="V265" s="14" t="n">
-        <v>1.3062</v>
-      </c>
-      <c r="W265" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X265" s="14" t="n">
-        <v>0.6895</v>
-      </c>
-      <c r="Y265" s="14" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="Z265" s="14" t="n">
-        <v>-16.52</v>
-      </c>
-      <c r="AA265" s="14" t="n">
-        <v>1.9135</v>
-      </c>
-      <c r="AB265" s="14" t="n">
-        <v>1.4649</v>
-      </c>
-      <c r="AC265" s="14" t="n">
-        <v>1.6035</v>
-      </c>
-      <c r="AD265" s="14" t="n">
-        <v>1.027488323272699</v>
-      </c>
+      <c r="V265" s="14" t="inlineStr"/>
+      <c r="W265" s="14" t="inlineStr"/>
+      <c r="X265" s="14" t="inlineStr"/>
+      <c r="Y265" s="14" t="inlineStr"/>
+      <c r="Z265" s="14" t="inlineStr"/>
+      <c r="AA265" s="14" t="inlineStr"/>
+      <c r="AB265" s="14" t="inlineStr"/>
+      <c r="AC265" s="14" t="inlineStr"/>
+      <c r="AD265" s="14" t="inlineStr"/>
       <c r="AE265" s="14" t="n">
         <v>30678.18</v>
       </c>
       <c r="AF265" s="14" t="n"/>
-      <c r="AG265" s="14" t="n">
-        <v>0.003231</v>
-      </c>
+      <c r="AG265" s="14" t="n"/>
       <c r="AH265" s="14" t="inlineStr"/>
       <c r="AI265" s="14" t="inlineStr">
         <is>
@@ -38225,7 +37489,7 @@
       </c>
       <c r="AP265" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ265" s="14" t="inlineStr"/>
@@ -38296,12 +37560,8 @@
       <c r="L266" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M266" s="14" t="n">
-        <v>10278462.94253092</v>
-      </c>
-      <c r="N266" s="14" t="n">
-        <v>43490842</v>
-      </c>
+      <c r="M266" s="14" t="inlineStr"/>
+      <c r="N266" s="14" t="inlineStr"/>
       <c r="O266" s="14" t="b">
         <v>1</v>
       </c>
@@ -38321,40 +37581,20 @@
       <c r="U266" s="14" t="n">
         <v>2.68</v>
       </c>
-      <c r="V266" s="14" t="n">
-        <v>1.407</v>
-      </c>
-      <c r="W266" s="14" t="n">
-        <v>1.3363</v>
-      </c>
-      <c r="X266" s="14" t="n">
-        <v>0.7837</v>
-      </c>
-      <c r="Y266" s="14" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="Z266" s="14" t="n">
-        <v>-19</v>
-      </c>
-      <c r="AA266" s="14" t="n">
-        <v>1.9068</v>
-      </c>
-      <c r="AB266" s="14" t="n">
-        <v>1.3552</v>
-      </c>
-      <c r="AC266" s="14" t="n">
-        <v>1.5253</v>
-      </c>
-      <c r="AD266" s="14" t="n">
-        <v>0.905838599867248</v>
-      </c>
+      <c r="V266" s="14" t="inlineStr"/>
+      <c r="W266" s="14" t="inlineStr"/>
+      <c r="X266" s="14" t="inlineStr"/>
+      <c r="Y266" s="14" t="inlineStr"/>
+      <c r="Z266" s="14" t="inlineStr"/>
+      <c r="AA266" s="14" t="inlineStr"/>
+      <c r="AB266" s="14" t="inlineStr"/>
+      <c r="AC266" s="14" t="inlineStr"/>
+      <c r="AD266" s="14" t="inlineStr"/>
       <c r="AE266" s="14" t="n">
         <v>53610.76</v>
       </c>
       <c r="AF266" s="14" t="n"/>
-      <c r="AG266" s="14" t="n">
-        <v>0.005216</v>
-      </c>
+      <c r="AG266" s="14" t="n"/>
       <c r="AH266" s="14" t="inlineStr"/>
       <c r="AI266" s="14" t="inlineStr">
         <is>
@@ -38389,7 +37629,7 @@
       </c>
       <c r="AP266" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ266" s="14" t="inlineStr"/>
@@ -38460,12 +37700,8 @@
       <c r="L267" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M267" s="14" t="n">
-        <v>9392689.251</v>
-      </c>
-      <c r="N267" s="14" t="n">
-        <v>43125295</v>
-      </c>
+      <c r="M267" s="14" t="inlineStr"/>
+      <c r="N267" s="14" t="inlineStr"/>
       <c r="O267" s="14" t="b">
         <v>1</v>
       </c>
@@ -38485,40 +37721,20 @@
       <c r="U267" s="14" t="n">
         <v>1.29</v>
       </c>
-      <c r="V267" s="14" t="n">
-        <v>1.1385</v>
-      </c>
-      <c r="W267" s="14" t="n">
-        <v>1.2748</v>
-      </c>
-      <c r="X267" s="14" t="n">
-        <v>0.9199000000000001</v>
-      </c>
-      <c r="Y267" s="14" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="Z267" s="14" t="n">
-        <v>13.46</v>
-      </c>
-      <c r="AA267" s="14" t="n">
-        <v>1.8797</v>
-      </c>
-      <c r="AB267" s="14" t="n">
-        <v>1.6511</v>
-      </c>
-      <c r="AC267" s="14" t="n">
-        <v>1.8074</v>
-      </c>
-      <c r="AD267" s="14" t="n">
-        <v>0.9635347183991276</v>
-      </c>
+      <c r="V267" s="14" t="inlineStr"/>
+      <c r="W267" s="14" t="inlineStr"/>
+      <c r="X267" s="14" t="inlineStr"/>
+      <c r="Y267" s="14" t="inlineStr"/>
+      <c r="Z267" s="14" t="inlineStr"/>
+      <c r="AA267" s="14" t="inlineStr"/>
+      <c r="AB267" s="14" t="inlineStr"/>
+      <c r="AC267" s="14" t="inlineStr"/>
+      <c r="AD267" s="14" t="inlineStr"/>
       <c r="AE267" s="14" t="n">
         <v>63867.37</v>
       </c>
       <c r="AF267" s="14" t="n"/>
-      <c r="AG267" s="14" t="n">
-        <v>0.0068</v>
-      </c>
+      <c r="AG267" s="14" t="n"/>
       <c r="AH267" s="14" t="inlineStr"/>
       <c r="AI267" s="14" t="inlineStr">
         <is>
@@ -38553,7 +37769,7 @@
       </c>
       <c r="AP267" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ267" s="14" t="inlineStr"/>
@@ -38624,12 +37840,8 @@
       <c r="L268" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M268" s="14" t="n">
-        <v>9454299.656080641</v>
-      </c>
-      <c r="N268" s="14" t="n">
-        <v>42878272</v>
-      </c>
+      <c r="M268" s="14" t="inlineStr"/>
+      <c r="N268" s="14" t="inlineStr"/>
       <c r="O268" s="14" t="b">
         <v>1</v>
       </c>
@@ -38649,40 +37861,20 @@
       <c r="U268" s="14" t="n">
         <v>1.03</v>
       </c>
-      <c r="V268" s="14" t="n">
-        <v>1.1448</v>
-      </c>
-      <c r="W268" s="14" t="n">
-        <v>1.2193</v>
-      </c>
-      <c r="X268" s="14" t="n">
-        <v>1.0026</v>
-      </c>
-      <c r="Y268" s="14" t="n">
-        <v>-3.01</v>
-      </c>
-      <c r="Z268" s="14" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="AA268" s="14" t="n">
-        <v>1.8559</v>
-      </c>
-      <c r="AB268" s="14" t="n">
-        <v>1.6212</v>
-      </c>
-      <c r="AC268" s="14" t="n">
-        <v>1.8425</v>
-      </c>
-      <c r="AD268" s="14" t="n">
-        <v>0.9605577222110836</v>
-      </c>
+      <c r="V268" s="14" t="inlineStr"/>
+      <c r="W268" s="14" t="inlineStr"/>
+      <c r="X268" s="14" t="inlineStr"/>
+      <c r="Y268" s="14" t="inlineStr"/>
+      <c r="Z268" s="14" t="inlineStr"/>
+      <c r="AA268" s="14" t="inlineStr"/>
+      <c r="AB268" s="14" t="inlineStr"/>
+      <c r="AC268" s="14" t="inlineStr"/>
+      <c r="AD268" s="14" t="inlineStr"/>
       <c r="AE268" s="14" t="n">
         <v>47367.93</v>
       </c>
       <c r="AF268" s="14" t="n"/>
-      <c r="AG268" s="14" t="n">
-        <v>0.00501</v>
-      </c>
+      <c r="AG268" s="14" t="n"/>
       <c r="AH268" s="14" t="inlineStr"/>
       <c r="AI268" s="14" t="inlineStr">
         <is>
@@ -38717,7 +37909,7 @@
       </c>
       <c r="AP268" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ268" s="14" t="inlineStr"/>
@@ -38788,12 +37980,8 @@
       <c r="L269" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M269" s="14" t="n">
-        <v>9423426.367027201</v>
-      </c>
-      <c r="N269" s="14" t="n">
-        <v>43012689</v>
-      </c>
+      <c r="M269" s="14" t="inlineStr"/>
+      <c r="N269" s="14" t="inlineStr"/>
       <c r="O269" s="14" t="b">
         <v>1</v>
       </c>
@@ -38813,40 +38001,20 @@
       <c r="U269" s="14" t="n">
         <v>1.19</v>
       </c>
-      <c r="V269" s="14" t="n">
-        <v>1.1795</v>
-      </c>
-      <c r="W269" s="14" t="n">
-        <v>1.1538</v>
-      </c>
-      <c r="X269" s="14" t="n">
-        <v>1.0851</v>
-      </c>
-      <c r="Y269" s="14" t="n">
-        <v>-3.53</v>
-      </c>
-      <c r="Z269" s="14" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="AA269" s="14" t="n">
-        <v>1.8394</v>
-      </c>
-      <c r="AB269" s="14" t="n">
-        <v>1.5595</v>
-      </c>
-      <c r="AC269" s="14" t="n">
-        <v>1.7108</v>
-      </c>
-      <c r="AD269" s="14" t="n">
-        <v>1.200131229264558</v>
-      </c>
+      <c r="V269" s="14" t="inlineStr"/>
+      <c r="W269" s="14" t="inlineStr"/>
+      <c r="X269" s="14" t="inlineStr"/>
+      <c r="Y269" s="14" t="inlineStr"/>
+      <c r="Z269" s="14" t="inlineStr"/>
+      <c r="AA269" s="14" t="inlineStr"/>
+      <c r="AB269" s="14" t="inlineStr"/>
+      <c r="AC269" s="14" t="inlineStr"/>
+      <c r="AD269" s="14" t="inlineStr"/>
       <c r="AE269" s="14" t="n">
         <v>34199.73</v>
       </c>
       <c r="AF269" s="14" t="n"/>
-      <c r="AG269" s="14" t="n">
-        <v>0.003629</v>
-      </c>
+      <c r="AG269" s="14" t="n"/>
       <c r="AH269" s="14" t="inlineStr"/>
       <c r="AI269" s="14" t="inlineStr">
         <is>
@@ -38881,7 +38049,7 @@
       </c>
       <c r="AP269" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ269" s="14" t="inlineStr"/>
@@ -38952,12 +38120,8 @@
       <c r="L270" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M270" s="14" t="n">
-        <v>9719699.02154118</v>
-      </c>
-      <c r="N270" s="14" t="n">
-        <v>43996437</v>
-      </c>
+      <c r="M270" s="14" t="inlineStr"/>
+      <c r="N270" s="14" t="inlineStr"/>
       <c r="O270" s="14" t="b">
         <v>1</v>
       </c>
@@ -38977,40 +38141,20 @@
       <c r="U270" s="14" t="n">
         <v>1.27</v>
       </c>
-      <c r="V270" s="14" t="n">
-        <v>0.9908</v>
-      </c>
-      <c r="W270" s="14" t="n">
-        <v>1.0987</v>
-      </c>
-      <c r="X270" s="14" t="n">
-        <v>1.243</v>
-      </c>
-      <c r="Y270" s="14" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="Z270" s="14" t="n">
-        <v>12.72</v>
-      </c>
-      <c r="AA270" s="14" t="n">
-        <v>1.844</v>
-      </c>
-      <c r="AB270" s="14" t="n">
-        <v>1.8612</v>
-      </c>
-      <c r="AC270" s="14" t="n">
-        <v>1.9931</v>
-      </c>
-      <c r="AD270" s="14" t="n">
-        <v>0.9868165960607348</v>
-      </c>
+      <c r="V270" s="14" t="inlineStr"/>
+      <c r="W270" s="14" t="inlineStr"/>
+      <c r="X270" s="14" t="inlineStr"/>
+      <c r="Y270" s="14" t="inlineStr"/>
+      <c r="Z270" s="14" t="inlineStr"/>
+      <c r="AA270" s="14" t="inlineStr"/>
+      <c r="AB270" s="14" t="inlineStr"/>
+      <c r="AC270" s="14" t="inlineStr"/>
+      <c r="AD270" s="14" t="inlineStr"/>
       <c r="AE270" s="14" t="n">
         <v>40192.76</v>
       </c>
       <c r="AF270" s="14" t="n"/>
-      <c r="AG270" s="14" t="n">
-        <v>0.004135</v>
-      </c>
+      <c r="AG270" s="14" t="n"/>
       <c r="AH270" s="14" t="inlineStr"/>
       <c r="AI270" s="14" t="inlineStr">
         <is>
@@ -39045,7 +38189,7 @@
       </c>
       <c r="AP270" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ270" s="14" t="inlineStr"/>
@@ -39071,9 +38215,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX270" s="17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX270" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -39116,12 +38260,8 @@
       <c r="L271" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M271" s="14" t="n">
-        <v>9377763.65894456</v>
-      </c>
-      <c r="N271" s="14" t="n">
-        <v>44131342</v>
-      </c>
+      <c r="M271" s="14" t="inlineStr"/>
+      <c r="N271" s="14" t="inlineStr"/>
       <c r="O271" s="14" t="b">
         <v>1</v>
       </c>
@@ -39141,40 +38281,20 @@
       <c r="U271" s="14" t="n">
         <v>0.6</v>
       </c>
-      <c r="V271" s="14" t="n">
-        <v>0.9344</v>
-      </c>
-      <c r="W271" s="14" t="n">
-        <v>1.0254</v>
-      </c>
-      <c r="X271" s="14" t="n">
-        <v>1.358</v>
-      </c>
-      <c r="Y271" s="14" t="n">
-        <v>-2.83</v>
-      </c>
-      <c r="Z271" s="14" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="AA271" s="14" t="n">
-        <v>1.8034</v>
-      </c>
-      <c r="AB271" s="14" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC271" s="14" t="n">
-        <v>2.0713</v>
-      </c>
-      <c r="AD271" s="14" t="n">
-        <v>1.013091468576515</v>
-      </c>
+      <c r="V271" s="14" t="inlineStr"/>
+      <c r="W271" s="14" t="inlineStr"/>
+      <c r="X271" s="14" t="inlineStr"/>
+      <c r="Y271" s="14" t="inlineStr"/>
+      <c r="Z271" s="14" t="inlineStr"/>
+      <c r="AA271" s="14" t="inlineStr"/>
+      <c r="AB271" s="14" t="inlineStr"/>
+      <c r="AC271" s="14" t="inlineStr"/>
+      <c r="AD271" s="14" t="inlineStr"/>
       <c r="AE271" s="14" t="n">
         <v>23984.96</v>
       </c>
       <c r="AF271" s="14" t="n"/>
-      <c r="AG271" s="14" t="n">
-        <v>0.002558</v>
-      </c>
+      <c r="AG271" s="14" t="n"/>
       <c r="AH271" s="14" t="inlineStr"/>
       <c r="AI271" s="14" t="inlineStr">
         <is>
@@ -39209,7 +38329,7 @@
       </c>
       <c r="AP271" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>MISSING(&gt;30d)</t>
         </is>
       </c>
       <c r="AQ271" s="14" t="inlineStr"/>
@@ -39301,39 +38421,19 @@
       <c r="S272" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T272" s="14" t="n">
-        <v>1.017</v>
-      </c>
+      <c r="T272" s="14" t="inlineStr"/>
       <c r="U272" s="14" t="n">
         <v>0.6</v>
       </c>
-      <c r="V272" s="14" t="n">
-        <v>0.9367</v>
-      </c>
-      <c r="W272" s="14" t="n">
-        <v>0.9536</v>
-      </c>
-      <c r="X272" s="14" t="n">
-        <v>1.1607</v>
-      </c>
-      <c r="Y272" s="14" t="n">
-        <v>-2.67</v>
-      </c>
-      <c r="Z272" s="14" t="n">
-        <v>22.55</v>
-      </c>
-      <c r="AA272" s="14" t="n">
-        <v>1.7902</v>
-      </c>
-      <c r="AB272" s="14" t="n">
-        <v>1.9112</v>
-      </c>
-      <c r="AC272" s="14" t="n">
-        <v>2.0979</v>
-      </c>
-      <c r="AD272" s="14" t="n">
-        <v>0.85381705643743</v>
-      </c>
+      <c r="V272" s="14" t="inlineStr"/>
+      <c r="W272" s="14" t="inlineStr"/>
+      <c r="X272" s="14" t="inlineStr"/>
+      <c r="Y272" s="14" t="inlineStr"/>
+      <c r="Z272" s="14" t="inlineStr"/>
+      <c r="AA272" s="14" t="inlineStr"/>
+      <c r="AB272" s="14" t="inlineStr"/>
+      <c r="AC272" s="14" t="inlineStr"/>
+      <c r="AD272" s="14" t="inlineStr"/>
       <c r="AE272" s="14" t="n">
         <v>38075.58</v>
       </c>
@@ -39375,7 +38475,7 @@
       </c>
       <c r="AP272" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ272" s="14" t="inlineStr"/>
@@ -39467,39 +38567,19 @@
       <c r="S273" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T273" s="14" t="n">
-        <v>1.007</v>
-      </c>
+      <c r="T273" s="14" t="inlineStr"/>
       <c r="U273" s="14" t="n">
         <v>0.47</v>
       </c>
-      <c r="V273" s="14" t="n">
-        <v>0.9992</v>
-      </c>
-      <c r="W273" s="14" t="n">
-        <v>0.9557</v>
-      </c>
-      <c r="X273" s="14" t="n">
-        <v>1.0587</v>
-      </c>
-      <c r="Y273" s="14" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="Z273" s="14" t="n">
-        <v>-4.11</v>
-      </c>
-      <c r="AA273" s="14" t="n">
-        <v>1.7833</v>
-      </c>
-      <c r="AB273" s="14" t="n">
-        <v>1.7847</v>
-      </c>
-      <c r="AC273" s="14" t="n">
-        <v>1.9507</v>
-      </c>
-      <c r="AD273" s="14" t="n">
-        <v>0.9158730737407392</v>
-      </c>
+      <c r="V273" s="14" t="inlineStr"/>
+      <c r="W273" s="14" t="inlineStr"/>
+      <c r="X273" s="14" t="inlineStr"/>
+      <c r="Y273" s="14" t="inlineStr"/>
+      <c r="Z273" s="14" t="inlineStr"/>
+      <c r="AA273" s="14" t="inlineStr"/>
+      <c r="AB273" s="14" t="inlineStr"/>
+      <c r="AC273" s="14" t="inlineStr"/>
+      <c r="AD273" s="14" t="inlineStr"/>
       <c r="AE273" s="14" t="n">
         <v>16946.91</v>
       </c>
@@ -39541,7 +38621,7 @@
       </c>
       <c r="AP273" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ273" s="14" t="inlineStr"/>
@@ -39633,39 +38713,19 @@
       <c r="S274" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T274" s="14" t="n">
-        <v>0.997</v>
-      </c>
+      <c r="T274" s="14" t="inlineStr"/>
       <c r="U274" s="14" t="n">
         <v>0.53</v>
       </c>
-      <c r="V274" s="14" t="n">
-        <v>1.0332</v>
-      </c>
-      <c r="W274" s="14" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="X274" s="14" t="n">
-        <v>1.151</v>
-      </c>
-      <c r="Y274" s="14" t="n">
-        <v>-1.31</v>
-      </c>
-      <c r="Z274" s="14" t="n">
-        <v>-10.75</v>
-      </c>
-      <c r="AA274" s="14" t="n">
-        <v>1.7798</v>
-      </c>
-      <c r="AB274" s="14" t="n">
-        <v>1.7226</v>
-      </c>
-      <c r="AC274" s="14" t="n">
-        <v>1.9691</v>
-      </c>
-      <c r="AD274" s="14" t="n">
-        <v>0.8756275490872794</v>
-      </c>
+      <c r="V274" s="14" t="inlineStr"/>
+      <c r="W274" s="14" t="inlineStr"/>
+      <c r="X274" s="14" t="inlineStr"/>
+      <c r="Y274" s="14" t="inlineStr"/>
+      <c r="Z274" s="14" t="inlineStr"/>
+      <c r="AA274" s="14" t="inlineStr"/>
+      <c r="AB274" s="14" t="inlineStr"/>
+      <c r="AC274" s="14" t="inlineStr"/>
+      <c r="AD274" s="14" t="inlineStr"/>
       <c r="AE274" s="14" t="n">
         <v>29644.95</v>
       </c>
@@ -39707,12 +38767,10 @@
       </c>
       <c r="AP274" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
-        </is>
-      </c>
-      <c r="AQ274" s="14" t="n">
-        <v>0.09660000000000001</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ274" s="14" t="inlineStr"/>
       <c r="AR274" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -39801,39 +38859,19 @@
       <c r="S275" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T275" s="14" t="n">
-        <v>0.99</v>
-      </c>
+      <c r="T275" s="14" t="inlineStr"/>
       <c r="U275" s="14" t="n">
         <v>0.54</v>
       </c>
-      <c r="V275" s="14" t="n">
-        <v>1.0557</v>
-      </c>
-      <c r="W275" s="14" t="n">
-        <v>1.0289</v>
-      </c>
-      <c r="X275" s="14" t="n">
-        <v>0.967</v>
-      </c>
-      <c r="Y275" s="14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z275" s="14" t="n">
-        <v>-10.56</v>
-      </c>
-      <c r="AA275" s="14" t="n">
-        <v>1.8045</v>
-      </c>
-      <c r="AB275" s="14" t="n">
-        <v>1.7093</v>
-      </c>
-      <c r="AC275" s="14" t="n">
-        <v>1.9274</v>
-      </c>
-      <c r="AD275" s="14" t="n">
-        <v>0.7407839683808324</v>
-      </c>
+      <c r="V275" s="14" t="inlineStr"/>
+      <c r="W275" s="14" t="inlineStr"/>
+      <c r="X275" s="14" t="inlineStr"/>
+      <c r="Y275" s="14" t="inlineStr"/>
+      <c r="Z275" s="14" t="inlineStr"/>
+      <c r="AA275" s="14" t="inlineStr"/>
+      <c r="AB275" s="14" t="inlineStr"/>
+      <c r="AC275" s="14" t="inlineStr"/>
+      <c r="AD275" s="14" t="inlineStr"/>
       <c r="AE275" s="14" t="n">
         <v>21265.7</v>
       </c>
@@ -39875,12 +38913,10 @@
       </c>
       <c r="AP275" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
-        </is>
-      </c>
-      <c r="AQ275" s="14" t="n">
-        <v>0.0064</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ275" s="14" t="inlineStr"/>
       <c r="AR275" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -39969,39 +39005,19 @@
       <c r="S276" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T276" s="14" t="n">
-        <v>0.951</v>
-      </c>
+      <c r="T276" s="14" t="inlineStr"/>
       <c r="U276" s="14" t="n">
         <v>4.21</v>
       </c>
-      <c r="V276" s="14" t="n">
-        <v>1.0954</v>
-      </c>
-      <c r="W276" s="14" t="n">
-        <v>1.0611</v>
-      </c>
-      <c r="X276" s="14" t="n">
-        <v>0.8899</v>
-      </c>
-      <c r="Y276" s="14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z276" s="14" t="n">
-        <v>-6.42</v>
-      </c>
-      <c r="AA276" s="14" t="n">
-        <v>1.8296</v>
-      </c>
-      <c r="AB276" s="14" t="n">
-        <v>1.6702</v>
-      </c>
-      <c r="AC276" s="14" t="n">
-        <v>1.8433</v>
-      </c>
-      <c r="AD276" s="14" t="n">
-        <v>0.9041377382073656</v>
-      </c>
+      <c r="V276" s="14" t="inlineStr"/>
+      <c r="W276" s="14" t="inlineStr"/>
+      <c r="X276" s="14" t="inlineStr"/>
+      <c r="Y276" s="14" t="inlineStr"/>
+      <c r="Z276" s="14" t="inlineStr"/>
+      <c r="AA276" s="14" t="inlineStr"/>
+      <c r="AB276" s="14" t="inlineStr"/>
+      <c r="AC276" s="14" t="inlineStr"/>
+      <c r="AD276" s="14" t="inlineStr"/>
       <c r="AE276" s="14" t="n">
         <v>108217.22</v>
       </c>
@@ -40043,12 +39059,10 @@
       </c>
       <c r="AP276" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
-        </is>
-      </c>
-      <c r="AQ276" s="14" t="n">
-        <v>0</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ276" s="14" t="inlineStr"/>
       <c r="AR276" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -40137,9 +39151,7 @@
       <c r="S277" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T277" s="14" t="n">
-        <v>0.96</v>
-      </c>
+      <c r="T277" s="14" t="inlineStr"/>
       <c r="U277" s="14" t="n">
         <v>7.36</v>
       </c>
@@ -40193,12 +39205,10 @@
       </c>
       <c r="AP277" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
-        </is>
-      </c>
-      <c r="AQ277" s="14" t="n">
-        <v>0.0623</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ277" s="14" t="inlineStr"/>
       <c r="AR277" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -40287,9 +39297,7 @@
       <c r="S278" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="T278" s="14" t="n">
-        <v>1.002</v>
-      </c>
+      <c r="T278" s="14" t="inlineStr"/>
       <c r="U278" s="14" t="n">
         <v>1.35</v>
       </c>
@@ -40343,12 +39351,10 @@
       </c>
       <c r="AP278" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
-        </is>
-      </c>
-      <c r="AQ278" s="14" t="n">
-        <v>0.3681</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ278" s="14" t="inlineStr"/>
       <c r="AR278" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -40438,7 +39444,7 @@
         <v>0</v>
       </c>
       <c r="T279" s="14" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="U279" s="14" t="n">
         <v>0.57</v>
@@ -40493,12 +39499,10 @@
       </c>
       <c r="AP279" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
-        </is>
-      </c>
-      <c r="AQ279" s="14" t="n">
-        <v>0.2156</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ279" s="14" t="inlineStr"/>
       <c r="AR279" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -40588,32 +39592,20 @@
         <v>0</v>
       </c>
       <c r="T280" s="14" t="n">
-        <v>0.957</v>
+        <v>0.959</v>
       </c>
       <c r="U280" s="14" t="n">
         <v>0.61</v>
       </c>
-      <c r="V280" s="14" t="n">
-        <v>1.4783</v>
-      </c>
+      <c r="V280" s="14" t="inlineStr"/>
       <c r="W280" s="14" t="inlineStr"/>
-      <c r="X280" s="14" t="n">
-        <v>0.5786</v>
-      </c>
+      <c r="X280" s="14" t="inlineStr"/>
       <c r="Y280" s="14" t="inlineStr"/>
       <c r="Z280" s="14" t="inlineStr"/>
-      <c r="AA280" s="14" t="n">
-        <v>1.6989</v>
-      </c>
-      <c r="AB280" s="14" t="n">
-        <v>1.1492</v>
-      </c>
-      <c r="AC280" s="14" t="n">
-        <v>1.1151</v>
-      </c>
-      <c r="AD280" s="14" t="n">
-        <v>0.8628</v>
-      </c>
+      <c r="AA280" s="14" t="inlineStr"/>
+      <c r="AB280" s="14" t="inlineStr"/>
+      <c r="AC280" s="14" t="inlineStr"/>
+      <c r="AD280" s="14" t="inlineStr"/>
       <c r="AE280" s="14" t="n">
         <v>43854.05</v>
       </c>
@@ -40655,12 +39647,10 @@
       </c>
       <c r="AP280" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
-        </is>
-      </c>
-      <c r="AQ280" s="14" t="n">
-        <v>0.0283</v>
-      </c>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ280" s="14" t="inlineStr"/>
       <c r="AR280" s="14" t="inlineStr">
         <is>
           <t>false</t>
@@ -40750,32 +39740,20 @@
         <v>0</v>
       </c>
       <c r="T281" s="14" t="n">
-        <v>0.954</v>
+        <v>0.957</v>
       </c>
       <c r="U281" s="14" t="n">
         <v>0.63</v>
       </c>
-      <c r="V281" s="14" t="n">
-        <v>1.5027</v>
-      </c>
+      <c r="V281" s="14" t="inlineStr"/>
       <c r="W281" s="14" t="inlineStr"/>
-      <c r="X281" s="14" t="n">
-        <v>0.6277</v>
-      </c>
+      <c r="X281" s="14" t="inlineStr"/>
       <c r="Y281" s="14" t="inlineStr"/>
       <c r="Z281" s="14" t="inlineStr"/>
-      <c r="AA281" s="14" t="n">
-        <v>1.7192</v>
-      </c>
-      <c r="AB281" s="14" t="n">
-        <v>1.1441</v>
-      </c>
-      <c r="AC281" s="14" t="n">
-        <v>1.157</v>
-      </c>
-      <c r="AD281" s="14" t="n">
-        <v>0.9897</v>
-      </c>
+      <c r="AA281" s="14" t="inlineStr"/>
+      <c r="AB281" s="14" t="inlineStr"/>
+      <c r="AC281" s="14" t="inlineStr"/>
+      <c r="AD281" s="14" t="inlineStr"/>
       <c r="AE281" s="14" t="n">
         <v>31952.26</v>
       </c>
@@ -40817,7 +39795,7 @@
       </c>
       <c r="AP281" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ281" s="14" t="n">
@@ -40912,32 +39890,20 @@
         <v>0</v>
       </c>
       <c r="T282" s="14" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="U282" s="14" t="n">
         <v>0.83</v>
       </c>
-      <c r="V282" s="14" t="n">
-        <v>1.426</v>
-      </c>
-      <c r="W282" s="14" t="n">
-        <v>1.4678</v>
-      </c>
+      <c r="V282" s="14" t="inlineStr"/>
+      <c r="W282" s="14" t="inlineStr"/>
       <c r="X282" s="14" t="inlineStr"/>
       <c r="Y282" s="14" t="inlineStr"/>
       <c r="Z282" s="14" t="inlineStr"/>
-      <c r="AA282" s="14" t="n">
-        <v>1.7807</v>
-      </c>
-      <c r="AB282" s="14" t="n">
-        <v>1.2487</v>
-      </c>
-      <c r="AC282" s="14" t="n">
-        <v>1.3111</v>
-      </c>
-      <c r="AD282" s="14" t="n">
-        <v>0.9313</v>
-      </c>
+      <c r="AA282" s="14" t="inlineStr"/>
+      <c r="AB282" s="14" t="inlineStr"/>
+      <c r="AC282" s="14" t="inlineStr"/>
+      <c r="AD282" s="14" t="inlineStr"/>
       <c r="AE282" s="14" t="n">
         <v>32456.37</v>
       </c>
@@ -40979,7 +39945,7 @@
       </c>
       <c r="AP282" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ282" s="14" t="n">
@@ -41074,36 +40040,20 @@
         <v>0</v>
       </c>
       <c r="T283" s="14" t="n">
-        <v>0.949</v>
+        <v>0.96</v>
       </c>
       <c r="U283" s="14" t="n">
         <v>0.58</v>
       </c>
-      <c r="V283" s="14" t="n">
-        <v>1.4844</v>
-      </c>
-      <c r="W283" s="14" t="n">
-        <v>1.47</v>
-      </c>
+      <c r="V283" s="14" t="inlineStr"/>
+      <c r="W283" s="14" t="inlineStr"/>
       <c r="X283" s="14" t="inlineStr"/>
-      <c r="Y283" s="14" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="Z283" s="14" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="AA283" s="14" t="n">
-        <v>1.7982</v>
-      </c>
-      <c r="AB283" s="14" t="n">
-        <v>1.2114</v>
-      </c>
-      <c r="AC283" s="14" t="n">
-        <v>1.3031</v>
-      </c>
-      <c r="AD283" s="14" t="n">
-        <v>1.0004</v>
-      </c>
+      <c r="Y283" s="14" t="inlineStr"/>
+      <c r="Z283" s="14" t="inlineStr"/>
+      <c r="AA283" s="14" t="inlineStr"/>
+      <c r="AB283" s="14" t="inlineStr"/>
+      <c r="AC283" s="14" t="inlineStr"/>
+      <c r="AD283" s="14" t="inlineStr"/>
       <c r="AE283" s="14" t="n">
         <v>16646.09</v>
       </c>
@@ -41145,11 +40095,11 @@
       </c>
       <c r="AP283" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ283" s="14" t="n">
-        <v>0.076</v>
+        <v>0.1369</v>
       </c>
       <c r="AR283" s="14" t="inlineStr">
         <is>
@@ -41244,36 +40194,20 @@
         <v>0</v>
       </c>
       <c r="T284" s="14" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.959</v>
       </c>
       <c r="U284" s="14" t="n">
         <v>0.59</v>
       </c>
-      <c r="V284" s="14" t="n">
-        <v>1.3519</v>
-      </c>
-      <c r="W284" s="14" t="n">
-        <v>1.4189</v>
-      </c>
+      <c r="V284" s="14" t="inlineStr"/>
+      <c r="W284" s="14" t="inlineStr"/>
       <c r="X284" s="14" t="inlineStr"/>
-      <c r="Y284" s="14" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="Z284" s="14" t="n">
-        <v>15.06</v>
-      </c>
-      <c r="AA284" s="14" t="n">
-        <v>1.7796</v>
-      </c>
-      <c r="AB284" s="14" t="n">
-        <v>1.3164</v>
-      </c>
-      <c r="AC284" s="14" t="n">
-        <v>1.3872</v>
-      </c>
-      <c r="AD284" s="14" t="n">
-        <v>1.0206</v>
-      </c>
+      <c r="Y284" s="14" t="inlineStr"/>
+      <c r="Z284" s="14" t="inlineStr"/>
+      <c r="AA284" s="14" t="inlineStr"/>
+      <c r="AB284" s="14" t="inlineStr"/>
+      <c r="AC284" s="14" t="inlineStr"/>
+      <c r="AD284" s="14" t="inlineStr"/>
       <c r="AE284" s="14" t="n">
         <v>19251.05</v>
       </c>
@@ -41315,11 +40249,11 @@
       </c>
       <c r="AP284" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ284" s="14" t="n">
-        <v>0.0023</v>
+        <v>0.0042</v>
       </c>
       <c r="AR284" s="14" t="inlineStr">
         <is>
@@ -41410,38 +40344,20 @@
         <v>0</v>
       </c>
       <c r="T285" s="14" t="n">
-        <v>0.966</v>
+        <v>0.976</v>
       </c>
       <c r="U285" s="14" t="n">
         <v>4.2</v>
       </c>
-      <c r="V285" s="14" t="n">
-        <v>1.3546</v>
-      </c>
-      <c r="W285" s="14" t="n">
-        <v>1.3946</v>
-      </c>
-      <c r="X285" s="14" t="n">
-        <v>1.272</v>
-      </c>
-      <c r="Y285" s="14" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="Z285" s="14" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="AA285" s="14" t="n">
-        <v>1.7795</v>
-      </c>
-      <c r="AB285" s="14" t="n">
-        <v>1.3137</v>
-      </c>
-      <c r="AC285" s="14" t="n">
-        <v>1.4184</v>
-      </c>
-      <c r="AD285" s="14" t="n">
-        <v>0.9828</v>
-      </c>
+      <c r="V285" s="14" t="inlineStr"/>
+      <c r="W285" s="14" t="inlineStr"/>
+      <c r="X285" s="14" t="inlineStr"/>
+      <c r="Y285" s="14" t="inlineStr"/>
+      <c r="Z285" s="14" t="inlineStr"/>
+      <c r="AA285" s="14" t="inlineStr"/>
+      <c r="AB285" s="14" t="inlineStr"/>
+      <c r="AC285" s="14" t="inlineStr"/>
+      <c r="AD285" s="14" t="inlineStr"/>
       <c r="AE285" s="14" t="n">
         <v>37908.68</v>
       </c>
@@ -41483,11 +40399,11 @@
       </c>
       <c r="AP285" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ285" s="14" t="n">
-        <v>0.0462</v>
+        <v>0.0832</v>
       </c>
       <c r="AR285" s="14" t="inlineStr">
         <is>
@@ -41583,33 +40499,15 @@
       <c r="U286" s="14" t="n">
         <v>3.56</v>
       </c>
-      <c r="V286" s="14" t="n">
-        <v>2.2667</v>
-      </c>
-      <c r="W286" s="14" t="n">
-        <v>1.5564</v>
-      </c>
-      <c r="X286" s="14" t="n">
-        <v>0.7336</v>
-      </c>
-      <c r="Y286" s="14" t="n">
-        <v>-5.18</v>
-      </c>
-      <c r="Z286" s="14" t="n">
-        <v>-37.91</v>
-      </c>
-      <c r="AA286" s="14" t="n">
-        <v>1.705</v>
-      </c>
-      <c r="AB286" s="14" t="n">
-        <v>0.7522</v>
-      </c>
-      <c r="AC286" s="14" t="n">
-        <v>0.8488</v>
-      </c>
-      <c r="AD286" s="14" t="n">
-        <v>0.9375</v>
-      </c>
+      <c r="V286" s="14" t="inlineStr"/>
+      <c r="W286" s="14" t="inlineStr"/>
+      <c r="X286" s="14" t="inlineStr"/>
+      <c r="Y286" s="14" t="inlineStr"/>
+      <c r="Z286" s="14" t="inlineStr"/>
+      <c r="AA286" s="14" t="inlineStr"/>
+      <c r="AB286" s="14" t="inlineStr"/>
+      <c r="AC286" s="14" t="inlineStr"/>
+      <c r="AD286" s="14" t="inlineStr"/>
       <c r="AE286" s="14" t="n">
         <v>56878.22</v>
       </c>
@@ -41651,7 +40549,7 @@
       </c>
       <c r="AP286" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ286" s="14" t="n">
@@ -41751,33 +40649,15 @@
       <c r="U287" s="14" t="n">
         <v>1.64</v>
       </c>
-      <c r="V287" s="14" t="n">
-        <v>2.2188</v>
-      </c>
-      <c r="W287" s="14" t="n">
-        <v>1.838</v>
-      </c>
-      <c r="X287" s="14" t="n">
-        <v>0.7137</v>
-      </c>
-      <c r="Y287" s="14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Z287" s="14" t="n">
-        <v>-37.62</v>
-      </c>
-      <c r="AA287" s="14" t="n">
-        <v>1.8221</v>
-      </c>
-      <c r="AB287" s="14" t="n">
-        <v>0.8212</v>
-      </c>
-      <c r="AC287" s="14" t="n">
-        <v>0.9357</v>
-      </c>
-      <c r="AD287" s="14" t="n">
-        <v>1.0287</v>
-      </c>
+      <c r="V287" s="14" t="inlineStr"/>
+      <c r="W287" s="14" t="inlineStr"/>
+      <c r="X287" s="14" t="inlineStr"/>
+      <c r="Y287" s="14" t="inlineStr"/>
+      <c r="Z287" s="14" t="inlineStr"/>
+      <c r="AA287" s="14" t="inlineStr"/>
+      <c r="AB287" s="14" t="inlineStr"/>
+      <c r="AC287" s="14" t="inlineStr"/>
+      <c r="AD287" s="14" t="inlineStr"/>
       <c r="AE287" s="14" t="n">
         <v>21515.26</v>
       </c>
@@ -41819,7 +40699,7 @@
       </c>
       <c r="AP287" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ287" s="14" t="n">
@@ -41851,9 +40731,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX287" s="17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX287" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -41923,33 +40803,15 @@
       <c r="U288" s="14" t="n">
         <v>0.9</v>
       </c>
-      <c r="V288" s="14" t="n">
-        <v>2.0306</v>
-      </c>
-      <c r="W288" s="14" t="n">
-        <v>2.1642</v>
-      </c>
-      <c r="X288" s="14" t="n">
-        <v>0.7889</v>
-      </c>
-      <c r="Y288" s="14" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="Z288" s="14" t="n">
-        <v>-30.58</v>
-      </c>
-      <c r="AA288" s="14" t="n">
-        <v>1.8519</v>
-      </c>
-      <c r="AB288" s="14" t="n">
-        <v>0.912</v>
-      </c>
-      <c r="AC288" s="14" t="n">
-        <v>1.028</v>
-      </c>
-      <c r="AD288" s="14" t="n">
-        <v>0.924</v>
-      </c>
+      <c r="V288" s="14" t="inlineStr"/>
+      <c r="W288" s="14" t="inlineStr"/>
+      <c r="X288" s="14" t="inlineStr"/>
+      <c r="Y288" s="14" t="inlineStr"/>
+      <c r="Z288" s="14" t="inlineStr"/>
+      <c r="AA288" s="14" t="inlineStr"/>
+      <c r="AB288" s="14" t="inlineStr"/>
+      <c r="AC288" s="14" t="inlineStr"/>
+      <c r="AD288" s="14" t="inlineStr"/>
       <c r="AE288" s="14" t="n">
         <v>16216.17</v>
       </c>
@@ -41991,7 +40853,7 @@
       </c>
       <c r="AP288" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ288" s="14" t="n">
@@ -42019,9 +40881,9 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AX288" s="17" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AX288" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
     </row>
@@ -42091,33 +40953,15 @@
       <c r="U289" s="14" t="n">
         <v>1.79</v>
       </c>
-      <c r="V289" s="14" t="n">
-        <v>1.5551</v>
-      </c>
-      <c r="W289" s="14" t="n">
-        <v>1.8955</v>
-      </c>
-      <c r="X289" s="14" t="n">
-        <v>0.8405</v>
-      </c>
-      <c r="Y289" s="14" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="Z289" s="14" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="AA289" s="14" t="n">
-        <v>1.7762</v>
-      </c>
-      <c r="AB289" s="14" t="n">
-        <v>1.1422</v>
-      </c>
-      <c r="AC289" s="14" t="n">
-        <v>1.1659</v>
-      </c>
-      <c r="AD289" s="14" t="n">
-        <v>0.9426</v>
-      </c>
+      <c r="V289" s="14" t="inlineStr"/>
+      <c r="W289" s="14" t="inlineStr"/>
+      <c r="X289" s="14" t="inlineStr"/>
+      <c r="Y289" s="14" t="inlineStr"/>
+      <c r="Z289" s="14" t="inlineStr"/>
+      <c r="AA289" s="14" t="inlineStr"/>
+      <c r="AB289" s="14" t="inlineStr"/>
+      <c r="AC289" s="14" t="inlineStr"/>
+      <c r="AD289" s="14" t="inlineStr"/>
       <c r="AE289" s="14" t="n">
         <v>29733.33</v>
       </c>
@@ -42141,9 +40985,9 @@
           <t>ABSTAIN(Nansen_LOCKED)</t>
         </is>
       </c>
-      <c r="AL289" s="18" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AL289" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
       <c r="AM289" s="14" t="inlineStr">
@@ -42151,11 +40995,7 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AN289" s="14" t="inlineStr">
-        <is>
-          <t>A(A1=True,A2-avg5gLSR=1.079,A3-slope=0.841,A4=True,A5-oicp=?) — spec v1.4 ky 08/08</t>
-        </is>
-      </c>
+      <c r="AN289" s="14" t="inlineStr"/>
       <c r="AO289" s="14" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -42163,7 +41003,7 @@
       </c>
       <c r="AP289" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ289" s="14" t="n">
@@ -42263,33 +41103,15 @@
       <c r="U290" s="14" t="n">
         <v>0.72</v>
       </c>
-      <c r="V290" s="14" t="n">
-        <v>1.9755</v>
-      </c>
-      <c r="W290" s="14" t="n">
-        <v>1.8302</v>
-      </c>
-      <c r="X290" s="14" t="n">
-        <v>0.6972</v>
-      </c>
-      <c r="Y290" s="14" t="n">
-        <v>-1.95</v>
-      </c>
-      <c r="Z290" s="14" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="AA290" s="14" t="n">
-        <v>1.7866</v>
-      </c>
-      <c r="AB290" s="14" t="n">
-        <v>0.9044</v>
-      </c>
-      <c r="AC290" s="14" t="n">
-        <v>0.9889</v>
-      </c>
-      <c r="AD290" s="14" t="n">
-        <v>1.0982</v>
-      </c>
+      <c r="V290" s="14" t="inlineStr"/>
+      <c r="W290" s="14" t="inlineStr"/>
+      <c r="X290" s="14" t="inlineStr"/>
+      <c r="Y290" s="14" t="inlineStr"/>
+      <c r="Z290" s="14" t="inlineStr"/>
+      <c r="AA290" s="14" t="inlineStr"/>
+      <c r="AB290" s="14" t="inlineStr"/>
+      <c r="AC290" s="14" t="inlineStr"/>
+      <c r="AD290" s="14" t="inlineStr"/>
       <c r="AE290" s="14" t="n">
         <v>50220.07</v>
       </c>
@@ -42313,9 +41135,9 @@
           <t>ABSTAIN(Nansen_LOCKED)</t>
         </is>
       </c>
-      <c r="AL290" s="18" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="AL290" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
         </is>
       </c>
       <c r="AM290" s="14" t="inlineStr">
@@ -42323,11 +41145,7 @@
           <t>false</t>
         </is>
       </c>
-      <c r="AN290" s="14" t="inlineStr">
-        <is>
-          <t>A(A1=True,A2-avg5gLSR=0.994,A3-slope=0.697,A4=False,A5-oicp=0.198) — spec v1.4 ky 08/08</t>
-        </is>
-      </c>
+      <c r="AN290" s="14" t="inlineStr"/>
       <c r="AO290" s="14" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
@@ -42335,7 +41153,7 @@
       </c>
       <c r="AP290" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ290" s="14" t="n">
@@ -42439,33 +41257,15 @@
       <c r="U291" s="14" t="n">
         <v>2.32</v>
       </c>
-      <c r="V291" s="14" t="n">
-        <v>1.6166</v>
-      </c>
-      <c r="W291" s="14" t="n">
-        <v>1.6959</v>
-      </c>
-      <c r="X291" s="14" t="n">
-        <v>1.4009</v>
-      </c>
-      <c r="Y291" s="14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z291" s="14" t="n">
-        <v>26.97</v>
-      </c>
-      <c r="AA291" s="14" t="n">
-        <v>1.872</v>
-      </c>
-      <c r="AB291" s="14" t="n">
-        <v>1.158</v>
-      </c>
-      <c r="AC291" s="14" t="n">
-        <v>1.1891</v>
-      </c>
-      <c r="AD291" s="14" t="n">
-        <v>1.0413</v>
-      </c>
+      <c r="V291" s="14" t="inlineStr"/>
+      <c r="W291" s="14" t="inlineStr"/>
+      <c r="X291" s="14" t="inlineStr"/>
+      <c r="Y291" s="14" t="inlineStr"/>
+      <c r="Z291" s="14" t="inlineStr"/>
+      <c r="AA291" s="14" t="inlineStr"/>
+      <c r="AB291" s="14" t="inlineStr"/>
+      <c r="AC291" s="14" t="inlineStr"/>
+      <c r="AD291" s="14" t="inlineStr"/>
       <c r="AE291" s="14" t="n">
         <v>75229.63</v>
       </c>
@@ -42507,7 +41307,7 @@
       </c>
       <c r="AP291" s="14" t="inlineStr">
         <is>
-          <t>freshwatch</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ291" s="14" t="n">
@@ -42657,7 +41457,7 @@
       </c>
       <c r="AP292" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ292" s="14" t="n">
@@ -42807,7 +41607,7 @@
       </c>
       <c r="AP293" s="14" t="inlineStr">
         <is>
-          <t>MISSING(&gt;30d)</t>
+          <t>fapi_LSR_30d</t>
         </is>
       </c>
       <c r="AQ293" s="14" t="n">
@@ -42842,417 +41642,1039 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
+      <c r="A294" s="14" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="B294" t="n">
-        <v>0.1967333333333333</v>
-      </c>
-      <c r="C294" t="n">
+      <c r="B294" s="14" t="n">
+        <v>0.19673333</v>
+      </c>
+      <c r="C294" s="14" t="n">
         <v>0.1992</v>
       </c>
-      <c r="D294" t="n">
+      <c r="D294" s="14" t="n">
         <v>0.2034</v>
       </c>
-      <c r="E294" t="n">
+      <c r="E294" s="14" t="n">
         <v>0.1891</v>
       </c>
-      <c r="F294" t="n">
+      <c r="F294" s="14" t="n">
         <v>0.1977</v>
       </c>
-      <c r="G294" t="n">
-        <v>1940969.2344</v>
-      </c>
-      <c r="H294" t="n">
-        <v>48.65836742084942</v>
-      </c>
-      <c r="I294" t="n">
-        <v>0.0002637483333333333</v>
-      </c>
-      <c r="J294" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="K294" t="n">
+      <c r="G294" s="14" t="n">
+        <v>1940969.23</v>
+      </c>
+      <c r="H294" s="14" t="inlineStr"/>
+      <c r="I294" s="14" t="n">
+        <v>0.00026375</v>
+      </c>
+      <c r="J294" s="14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K294" s="14" t="n">
         <v>0.00050001</v>
       </c>
-      <c r="L294" t="n">
+      <c r="L294" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M294" t="n">
+      <c r="M294" s="14" t="n">
         <v>9271101.8532</v>
       </c>
-      <c r="N294" t="n">
+      <c r="N294" s="14" t="n">
         <v>46565052</v>
       </c>
-      <c r="O294" t="n">
-        <v>1</v>
-      </c>
-      <c r="P294" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q294" t="n">
-        <v>-0.7031642390758475</v>
-      </c>
-      <c r="R294" t="n">
-        <v>0</v>
-      </c>
-      <c r="S294" t="n">
-        <v>0</v>
-      </c>
-      <c r="T294" t="n">
-        <v>1.043545329259211</v>
-      </c>
-      <c r="U294" t="n">
-        <v>0.719854330288357</v>
-      </c>
-      <c r="V294" t="n">
-        <v>2.131170973062122</v>
-      </c>
-      <c r="X294" t="n">
-        <v>0.8287160133802213</v>
-      </c>
-      <c r="Y294" t="n">
-        <v>3.541666666666656</v>
-      </c>
-      <c r="Z294" t="n">
-        <v>-21.4594127806563</v>
-      </c>
-      <c r="AA294" t="n">
-        <v>1.9383</v>
-      </c>
-      <c r="AB294" t="n">
-        <v>0.9095</v>
-      </c>
-      <c r="AC294" t="n">
-        <v>0.9661999999999999</v>
-      </c>
-      <c r="AD294" t="n">
-        <v>0.9491000000000001</v>
-      </c>
-      <c r="AE294" t="n">
+      <c r="O294" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P294" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q294" s="14" t="n">
+        <v>-0.70316424</v>
+      </c>
+      <c r="R294" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T294" s="14" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="U294" s="14" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="V294" s="14" t="inlineStr"/>
+      <c r="W294" s="14" t="inlineStr"/>
+      <c r="X294" s="14" t="inlineStr"/>
+      <c r="Y294" s="14" t="inlineStr"/>
+      <c r="Z294" s="14" t="inlineStr"/>
+      <c r="AA294" s="14" t="inlineStr"/>
+      <c r="AB294" s="14" t="inlineStr"/>
+      <c r="AC294" s="14" t="inlineStr"/>
+      <c r="AD294" s="14" t="inlineStr"/>
+      <c r="AE294" s="14" t="n">
         <v>31251.84</v>
       </c>
-      <c r="AG294" t="n">
+      <c r="AF294" s="14" t="n"/>
+      <c r="AG294" s="14" t="n">
         <v>0.003371</v>
       </c>
-      <c r="AK294" t="inlineStr">
-        <is>
-          <t>CoinGecko/BSC+ETH+Monad</t>
-        </is>
-      </c>
-      <c r="AO294" t="inlineStr">
-        <is>
-          <t>fapi.binance.com klines 1d</t>
-        </is>
-      </c>
-      <c r="AP294" t="inlineStr">
-        <is>
-          <t>fapi.binance.com topPos/topAcc/global/taker</t>
-        </is>
-      </c>
-      <c r="AQ294" t="n">
-        <v>0.3793651697184734</v>
-      </c>
-      <c r="AR294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW294" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX294" t="n">
-        <v>0</v>
+      <c r="AH294" s="14" t="inlineStr"/>
+      <c r="AI294" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ294" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK294" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL294" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM294" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN294" s="14" t="inlineStr"/>
+      <c r="AO294" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP294" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ294" s="14" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="AR294" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS294" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT294" s="14" t="inlineStr"/>
+      <c r="AU294" s="14" t="inlineStr"/>
+      <c r="AV294" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW294" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX294" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
+      <c r="A295" s="14" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="B295" t="n">
-        <v>0.2039666666666667</v>
-      </c>
-      <c r="C295" t="n">
+      <c r="B295" s="14" t="n">
+        <v>0.20396667</v>
+      </c>
+      <c r="C295" s="14" t="n">
         <v>0.1976</v>
       </c>
-      <c r="D295" t="n">
+      <c r="D295" s="14" t="n">
         <v>0.2079</v>
       </c>
-      <c r="E295" t="n">
+      <c r="E295" s="14" t="n">
         <v>0.1962</v>
       </c>
-      <c r="F295" t="n">
+      <c r="F295" s="14" t="n">
         <v>0.2078</v>
       </c>
-      <c r="G295" t="n">
-        <v>1965766.9715</v>
-      </c>
-      <c r="H295" t="n">
-        <v>47.98321707889169</v>
-      </c>
-      <c r="I295" t="n">
-        <v>0.000130415</v>
-      </c>
-      <c r="J295" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="K295" t="n">
+      <c r="G295" s="14" t="n">
+        <v>1965766.97</v>
+      </c>
+      <c r="H295" s="14" t="inlineStr"/>
+      <c r="I295" s="14" t="n">
+        <v>0.00017062</v>
+      </c>
+      <c r="J295" s="14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K295" s="14" t="n">
         <v>0.00033548</v>
       </c>
-      <c r="L295" t="n">
-        <v>6</v>
-      </c>
-      <c r="M295" t="n">
+      <c r="L295" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M295" s="14" t="n">
         <v>9095395.372033499</v>
       </c>
-      <c r="N295" t="n">
+      <c r="N295" s="14" t="n">
         <v>46019070</v>
       </c>
-      <c r="O295" t="n">
-        <v>1</v>
-      </c>
-      <c r="P295" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q295" t="n">
-        <v>5.108750632271131</v>
-      </c>
-      <c r="R295" t="n">
-        <v>0</v>
-      </c>
-      <c r="S295" t="n">
-        <v>0</v>
-      </c>
-      <c r="T295" t="n">
-        <v>1.023767995276133</v>
-      </c>
-      <c r="U295" t="n">
-        <v>0.7520151736142805</v>
-      </c>
-      <c r="V295" t="n">
-        <v>1.557080220850926</v>
-      </c>
-      <c r="W295" t="n">
-        <v>1.800943440287703</v>
-      </c>
-      <c r="X295" t="n">
-        <v>1.255536454646577</v>
-      </c>
-      <c r="Y295" t="n">
-        <v>-1.062786978279934</v>
-      </c>
-      <c r="Z295" t="n">
-        <v>35.41506322155031</v>
-      </c>
-      <c r="AA295" t="n">
-        <v>1.9177</v>
-      </c>
-      <c r="AB295" t="n">
-        <v>1.2316</v>
-      </c>
-      <c r="AC295" t="n">
-        <v>1.2416</v>
-      </c>
-      <c r="AD295" t="n">
-        <v>0.9226</v>
-      </c>
-      <c r="AE295" t="n">
+      <c r="O295" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P295" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q295" s="14" t="n">
+        <v>5.10875063</v>
+      </c>
+      <c r="R295" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S295" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T295" s="14" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="U295" s="14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="V295" s="14" t="inlineStr"/>
+      <c r="W295" s="14" t="inlineStr"/>
+      <c r="X295" s="14" t="inlineStr"/>
+      <c r="Y295" s="14" t="inlineStr"/>
+      <c r="Z295" s="14" t="inlineStr"/>
+      <c r="AA295" s="14" t="inlineStr"/>
+      <c r="AB295" s="14" t="inlineStr"/>
+      <c r="AC295" s="14" t="inlineStr"/>
+      <c r="AD295" s="14" t="inlineStr"/>
+      <c r="AE295" s="14" t="n">
         <v>26487.55</v>
       </c>
-      <c r="AG295" t="n">
+      <c r="AF295" s="14" t="n"/>
+      <c r="AG295" s="14" t="n">
         <v>0.002912</v>
       </c>
-      <c r="AK295" t="inlineStr">
-        <is>
-          <t>CoinGecko/BSC+ETH+Monad</t>
-        </is>
-      </c>
-      <c r="AO295" t="inlineStr">
-        <is>
-          <t>fapi.binance.com klines 1d</t>
-        </is>
-      </c>
-      <c r="AP295" t="inlineStr">
-        <is>
-          <t>fapi.binance.com topPos/topAcc/global/taker</t>
-        </is>
-      </c>
-      <c r="AQ295" t="n">
-        <v>0.3133809525063222</v>
-      </c>
-      <c r="AR295" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS295" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT295" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU295" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV295" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW295" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX295" t="n">
-        <v>0</v>
+      <c r="AH295" s="14" t="inlineStr"/>
+      <c r="AI295" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ295" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK295" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL295" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM295" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN295" s="14" t="inlineStr"/>
+      <c r="AO295" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP295" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ295" s="14" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="AR295" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS295" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT295" s="14" t="inlineStr"/>
+      <c r="AU295" s="14" t="inlineStr"/>
+      <c r="AV295" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW295" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX295" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
+      <c r="A296" s="14" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="B296" t="n">
-        <v>0.4822333333333333</v>
-      </c>
-      <c r="C296" t="n">
+      <c r="B296" s="14" t="n">
+        <v>0.48223333</v>
+      </c>
+      <c r="C296" s="14" t="n">
         <v>0.2076</v>
       </c>
-      <c r="D296" t="n">
+      <c r="D296" s="14" t="n">
         <v>0.6325</v>
       </c>
-      <c r="E296" t="n">
+      <c r="E296" s="14" t="n">
         <v>0.2068</v>
       </c>
-      <c r="F296" t="n">
+      <c r="F296" s="14" t="n">
         <v>0.6074000000000001</v>
       </c>
-      <c r="G296" t="n">
-        <v>903339470.6586699</v>
-      </c>
-      <c r="H296" t="n">
-        <v>51.95693523323135</v>
-      </c>
-      <c r="I296" t="n">
-        <v>0.0002265583333333333</v>
-      </c>
-      <c r="J296" t="n">
-        <v>5e-05</v>
-      </c>
-      <c r="K296" t="n">
+      <c r="G296" s="14" t="n">
+        <v>903339470.66</v>
+      </c>
+      <c r="H296" s="14" t="inlineStr"/>
+      <c r="I296" s="14" t="n">
+        <v>0.00026187</v>
+      </c>
+      <c r="J296" s="14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K296" s="14" t="n">
         <v>0.00060334</v>
       </c>
-      <c r="L296" t="n">
+      <c r="L296" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M296" s="14" t="n">
+        <v>9689917.191729</v>
+      </c>
+      <c r="N296" s="14" t="n">
+        <v>46642515</v>
+      </c>
+      <c r="O296" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P296" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q296" s="14" t="n">
+        <v>192.30028874</v>
+      </c>
+      <c r="R296" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S296" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T296" s="14" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="U296" s="14" t="n">
+        <v>345.58</v>
+      </c>
+      <c r="V296" s="14" t="inlineStr"/>
+      <c r="W296" s="14" t="inlineStr"/>
+      <c r="X296" s="14" t="inlineStr"/>
+      <c r="Y296" s="14" t="inlineStr"/>
+      <c r="Z296" s="14" t="inlineStr"/>
+      <c r="AA296" s="14" t="inlineStr"/>
+      <c r="AB296" s="14" t="inlineStr"/>
+      <c r="AC296" s="14" t="inlineStr"/>
+      <c r="AD296" s="14" t="inlineStr"/>
+      <c r="AE296" s="14" t="n">
+        <v>3928680.4</v>
+      </c>
+      <c r="AF296" s="14" t="n"/>
+      <c r="AG296" s="14" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="AH296" s="14" t="inlineStr"/>
+      <c r="AI296" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ296" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK296" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL296" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM296" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN296" s="14" t="inlineStr"/>
+      <c r="AO296" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP296" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ296" s="14" t="n">
+        <v>0.5366</v>
+      </c>
+      <c r="AR296" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS296" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT296" s="14" t="inlineStr"/>
+      <c r="AU296" s="14" t="inlineStr"/>
+      <c r="AV296" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW296" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX296" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B297" s="14" t="n">
+        <v>0.50736667</v>
+      </c>
+      <c r="C297" s="14" t="n">
+        <v>0.6074000000000001</v>
+      </c>
+      <c r="D297" s="14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E297" s="14" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="F297" s="14" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="G297" s="14" t="n">
+        <v>729196179.5599999</v>
+      </c>
+      <c r="H297" s="14" t="inlineStr"/>
+      <c r="I297" s="14" t="n">
+        <v>0.00049716</v>
+      </c>
+      <c r="J297" s="14" t="n">
+        <v>0.00029709</v>
+      </c>
+      <c r="K297" s="14" t="n">
+        <v>0.00096129</v>
+      </c>
+      <c r="L297" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="M296" t="n">
-        <v>9689917.191729</v>
-      </c>
-      <c r="N296" t="n">
-        <v>46642515</v>
-      </c>
-      <c r="O296" t="n">
-        <v>1</v>
-      </c>
-      <c r="P296" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q296" t="n">
-        <v>192.3002887391723</v>
-      </c>
-      <c r="R296" t="n">
-        <v>0</v>
-      </c>
-      <c r="S296" t="n">
-        <v>0</v>
-      </c>
-      <c r="T296" t="n">
-        <v>1.090686736749325</v>
-      </c>
-      <c r="U296" t="n">
-        <v>345.5775779677718</v>
-      </c>
-      <c r="V296" t="n">
-        <v>1.498530463102709</v>
-      </c>
-      <c r="W296" t="n">
-        <v>1.688970588235294</v>
-      </c>
-      <c r="X296" t="n">
-        <v>1.122109158186864</v>
-      </c>
-      <c r="Y296" t="n">
-        <v>-2.672444925966045</v>
-      </c>
-      <c r="Z296" t="n">
-        <v>38.41671247938427</v>
-      </c>
-      <c r="AA296" t="n">
-        <v>1.8865</v>
-      </c>
-      <c r="AB296" t="n">
-        <v>1.2589</v>
-      </c>
-      <c r="AC296" t="n">
-        <v>1.3343</v>
-      </c>
-      <c r="AD296" t="n">
-        <v>1.0745</v>
-      </c>
-      <c r="AE296" t="n">
-        <v>3928680.4</v>
-      </c>
-      <c r="AG296" t="n">
-        <v>0.40544</v>
-      </c>
-      <c r="AK296" t="inlineStr">
-        <is>
-          <t>CoinGecko/BSC+ETH+Monad</t>
-        </is>
-      </c>
-      <c r="AO296" t="inlineStr">
-        <is>
-          <t>fapi.binance.com klines 1d</t>
-        </is>
-      </c>
-      <c r="AP296" t="inlineStr">
-        <is>
-          <t>fapi.binance.com topPos/topAcc/global/taker</t>
-        </is>
-      </c>
-      <c r="AQ296" t="n">
-        <v>0.5366456643582297</v>
-      </c>
-      <c r="AR296" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS296" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT296" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU296" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV296" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW296" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX296" t="n">
-        <v>0</v>
+      <c r="M297" s="14" t="n">
+        <v>50466616.37049214</v>
+      </c>
+      <c r="N297" s="14" t="n">
+        <v>83210582</v>
+      </c>
+      <c r="O297" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P297" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q297" s="14" t="n">
+        <v>-17.59960487</v>
+      </c>
+      <c r="R297" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S297" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T297" s="14" t="n">
+        <v>5.607</v>
+      </c>
+      <c r="U297" s="14" t="n">
+        <v>203.39</v>
+      </c>
+      <c r="V297" s="14" t="inlineStr"/>
+      <c r="W297" s="14" t="inlineStr"/>
+      <c r="X297" s="14" t="inlineStr"/>
+      <c r="Y297" s="14" t="inlineStr"/>
+      <c r="Z297" s="14" t="inlineStr"/>
+      <c r="AA297" s="14" t="inlineStr"/>
+      <c r="AB297" s="14" t="inlineStr"/>
+      <c r="AC297" s="14" t="inlineStr"/>
+      <c r="AD297" s="14" t="inlineStr"/>
+      <c r="AE297" s="14" t="n">
+        <v>1844173.98</v>
+      </c>
+      <c r="AF297" s="14" t="n"/>
+      <c r="AG297" s="14" t="n">
+        <v>0.036542</v>
+      </c>
+      <c r="AH297" s="14" t="inlineStr"/>
+      <c r="AI297" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ297" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK297" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL297" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM297" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN297" s="14" t="inlineStr"/>
+      <c r="AO297" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP297" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ297" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR297" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS297" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT297" s="14" t="inlineStr"/>
+      <c r="AU297" s="14" t="inlineStr"/>
+      <c r="AV297" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW297" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX297" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B298" s="14" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="C298" s="14" t="n">
+        <v>0.5004999999999999</v>
+      </c>
+      <c r="D298" s="14" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="E298" s="14" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="F298" s="14" t="n">
+        <v>0.5109</v>
+      </c>
+      <c r="G298" s="14" t="n">
+        <v>251537949.54</v>
+      </c>
+      <c r="H298" s="14" t="inlineStr"/>
+      <c r="I298" s="14" t="n">
+        <v>0.00028687</v>
+      </c>
+      <c r="J298" s="14" t="n">
+        <v>0.00019455</v>
+      </c>
+      <c r="K298" s="14" t="n">
+        <v>0.00046983</v>
+      </c>
+      <c r="L298" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M298" s="14" t="n">
+        <v>35959036.8848256</v>
+      </c>
+      <c r="N298" s="14" t="n">
+        <v>71774976</v>
+      </c>
+      <c r="O298" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P298" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q298" s="14" t="n">
+        <v>2.07792208</v>
+      </c>
+      <c r="R298" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S298" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T298" s="14" t="n">
+        <v>3.916</v>
+      </c>
+      <c r="U298" s="14" t="n">
+        <v>60.59</v>
+      </c>
+      <c r="V298" s="14" t="inlineStr"/>
+      <c r="W298" s="14" t="inlineStr"/>
+      <c r="X298" s="14" t="inlineStr"/>
+      <c r="Y298" s="14" t="inlineStr"/>
+      <c r="Z298" s="14" t="inlineStr"/>
+      <c r="AA298" s="14" t="inlineStr"/>
+      <c r="AB298" s="14" t="inlineStr"/>
+      <c r="AC298" s="14" t="inlineStr"/>
+      <c r="AD298" s="14" t="inlineStr"/>
+      <c r="AE298" s="14" t="n">
+        <v>993186.77</v>
+      </c>
+      <c r="AF298" s="14" t="n"/>
+      <c r="AG298" s="14" t="n">
+        <v>0.02762</v>
+      </c>
+      <c r="AH298" s="14" t="inlineStr"/>
+      <c r="AI298" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ298" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK298" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL298" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM298" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN298" s="14" t="inlineStr"/>
+      <c r="AO298" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP298" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ298" s="14" t="n">
+        <v>0.6563</v>
+      </c>
+      <c r="AR298" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS298" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT298" s="14" t="inlineStr"/>
+      <c r="AU298" s="14" t="inlineStr"/>
+      <c r="AV298" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW298" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX298" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B299" s="14" t="n">
+        <v>0.28753333</v>
+      </c>
+      <c r="C299" s="14" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="D299" s="14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E299" s="14" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="F299" s="14" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="G299" s="14" t="n">
+        <v>300232871.59</v>
+      </c>
+      <c r="H299" s="14" t="inlineStr"/>
+      <c r="I299" s="14" t="n">
+        <v>0.00034166</v>
+      </c>
+      <c r="J299" s="14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K299" s="14" t="n">
+        <v>0.0006071</v>
+      </c>
+      <c r="L299" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="M299" s="14" t="n">
+        <v>35073195.6447</v>
+      </c>
+      <c r="N299" s="14" t="n">
+        <v>68596119</v>
+      </c>
+      <c r="O299" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P299" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q299" s="14" t="n">
+        <v>-68.29125073</v>
+      </c>
+      <c r="R299" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S299" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T299" s="14" t="n">
+        <v>3.775</v>
+      </c>
+      <c r="U299" s="14" t="n">
+        <v>63.46</v>
+      </c>
+      <c r="V299" s="14" t="inlineStr"/>
+      <c r="W299" s="14" t="inlineStr"/>
+      <c r="X299" s="14" t="inlineStr"/>
+      <c r="Y299" s="14" t="inlineStr"/>
+      <c r="Z299" s="14" t="inlineStr"/>
+      <c r="AA299" s="14" t="inlineStr"/>
+      <c r="AB299" s="14" t="inlineStr"/>
+      <c r="AC299" s="14" t="inlineStr"/>
+      <c r="AD299" s="14" t="inlineStr"/>
+      <c r="AE299" s="14" t="n">
+        <v>1709484.69</v>
+      </c>
+      <c r="AF299" s="14" t="n"/>
+      <c r="AG299" s="14" t="n">
+        <v>0.04874</v>
+      </c>
+      <c r="AH299" s="14" t="inlineStr"/>
+      <c r="AI299" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ299" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK299" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL299" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM299" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN299" s="14" t="inlineStr"/>
+      <c r="AO299" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP299" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ299" s="14" t="n">
+        <v>0.6353</v>
+      </c>
+      <c r="AR299" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS299" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT299" s="14" t="inlineStr"/>
+      <c r="AU299" s="14" t="inlineStr"/>
+      <c r="AV299" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW299" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX299" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="14" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B300" s="14" t="n">
+        <v>0.18886667</v>
+      </c>
+      <c r="C300" s="14" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="D300" s="14" t="n">
+        <v>0.2272</v>
+      </c>
+      <c r="E300" s="14" t="n">
+        <v>0.1432</v>
+      </c>
+      <c r="F300" s="14" t="n">
+        <v>0.1962</v>
+      </c>
+      <c r="G300" s="14" t="n">
+        <v>197861387.46</v>
+      </c>
+      <c r="H300" s="14" t="inlineStr"/>
+      <c r="I300" s="14" t="n">
+        <v>7.214e-05</v>
+      </c>
+      <c r="J300" s="14" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="K300" s="14" t="n">
+        <v>0.00012075</v>
+      </c>
+      <c r="L300" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M300" s="14" t="n">
+        <v>12695430.2316429</v>
+      </c>
+      <c r="N300" s="14" t="n">
+        <v>78401805</v>
+      </c>
+      <c r="O300" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P300" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q300" s="14" t="n">
+        <v>21.11111111</v>
+      </c>
+      <c r="R300" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S300" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T300" s="14" t="n">
+        <v>1.337</v>
+      </c>
+      <c r="U300" s="14" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="V300" s="14" t="inlineStr"/>
+      <c r="W300" s="14" t="inlineStr"/>
+      <c r="X300" s="14" t="inlineStr"/>
+      <c r="Y300" s="14" t="inlineStr"/>
+      <c r="Z300" s="14" t="inlineStr"/>
+      <c r="AA300" s="14" t="inlineStr"/>
+      <c r="AB300" s="14" t="inlineStr"/>
+      <c r="AC300" s="14" t="inlineStr"/>
+      <c r="AD300" s="14" t="inlineStr"/>
+      <c r="AE300" s="14" t="n">
+        <v>807345.28</v>
+      </c>
+      <c r="AF300" s="14" t="n"/>
+      <c r="AG300" s="14" t="n">
+        <v>0.063593</v>
+      </c>
+      <c r="AH300" s="14" t="inlineStr"/>
+      <c r="AI300" s="14" t="inlineStr">
+        <is>
+          <t>alpha_klines_store(forward_2026-08-04,venue=binance_alpha)</t>
+        </is>
+      </c>
+      <c r="AJ300" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(bapi_klines9==klines5_L48)</t>
+        </is>
+      </c>
+      <c r="AK300" s="14" t="inlineStr">
+        <is>
+          <t>ABSTAIN(Nansen_LOCKED)</t>
+        </is>
+      </c>
+      <c r="AL300" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AM300" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AN300" s="14" t="inlineStr"/>
+      <c r="AO300" s="14" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="AP300" s="14" t="inlineStr">
+        <is>
+          <t>fapi_LSR_30d</t>
+        </is>
+      </c>
+      <c r="AQ300" s="14" t="n">
+        <v>0.1051</v>
+      </c>
+      <c r="AR300" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AS300" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AT300" s="14" t="inlineStr"/>
+      <c r="AU300" s="14" t="inlineStr"/>
+      <c r="AV300" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AW300" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="AX300" s="14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -43278,7 +42700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -43337,7 +42759,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -43347,7 +42769,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>APRUSDT perp listed on Binance fapi (onboardDate)</t>
+          <t>APR perp onboard date unknown — CAN OPERATOR</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr"/>
@@ -44023,17 +43445,17 @@
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
         <is>
-          <t>VOL_8X_MED14</t>
+          <t>DUMP_GT10PCT</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=8.74x taker=49.3249 ret=16.196013%</t>
+          <t>ret_1d=-17.59960487% vol_vs_m=203.39 taker=None</t>
         </is>
       </c>
       <c r="D33" s="19" t="inlineStr">
@@ -44046,17 +43468,17 @@
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
         <is>
-          <t>VOL_8X_MED14</t>
+          <t>DUMP_GT10PCT</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=8.29x taker=48.6928 ret=2.603015%</t>
+          <t>ret_1d=-68.29125073% vol_vs_m=63.46 taker=None</t>
         </is>
       </c>
       <c r="D34" s="19" t="inlineStr">
@@ -44069,7 +43491,7 @@
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
@@ -44079,7 +43501,7 @@
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=58.38x taker=50.951 ret=29.005935%</t>
+          <t>vol_vs_med14=8.74x taker=49.3249 ret=16.196013%</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
@@ -44092,7 +43514,7 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
@@ -44102,7 +43524,7 @@
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=54.92x taker=50.4496 ret=-4.887867%</t>
+          <t>vol_vs_med14=8.29x taker=48.6928 ret=2.603015%</t>
         </is>
       </c>
       <c r="D36" s="19" t="inlineStr">
@@ -44115,7 +43537,7 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
@@ -44125,7 +43547,7 @@
       </c>
       <c r="C37" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=11.14x taker=51.1908 ret=6.62636%</t>
+          <t>vol_vs_med14=58.38x taker=50.951 ret=29.005935%</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
@@ -44138,7 +43560,7 @@
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
@@ -44148,7 +43570,7 @@
       </c>
       <c r="C38" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=9.88x taker=49.3232 ret=-25.069162%</t>
+          <t>vol_vs_med14=54.92x taker=50.4496 ret=-4.887867%</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
@@ -44161,7 +43583,7 @@
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
@@ -44171,7 +43593,7 @@
       </c>
       <c r="C39" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=10.73x taker=50.1944 ret=5.695696%</t>
+          <t>vol_vs_med14=11.14x taker=51.1908 ret=6.62636%</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
@@ -44184,7 +43606,7 @@
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
@@ -44194,7 +43616,7 @@
       </c>
       <c r="C40" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=20.22x taker=50.0116 ret=66.514935%</t>
+          <t>vol_vs_med14=9.88x taker=49.3232 ret=-25.069162%</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
@@ -44207,7 +43629,7 @@
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
@@ -44217,7 +43639,7 @@
       </c>
       <c r="C41" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=15.81x taker=48.1466 ret=-27.631539%</t>
+          <t>vol_vs_med14=10.73x taker=50.1944 ret=5.695696%</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
@@ -44230,7 +43652,7 @@
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
@@ -44240,7 +43662,7 @@
       </c>
       <c r="C42" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=50.95x taker=49.8378 ret=19.854068%</t>
+          <t>vol_vs_med14=20.22x taker=50.0116 ret=66.514935%</t>
         </is>
       </c>
       <c r="D42" s="19" t="inlineStr">
@@ -44253,7 +43675,7 @@
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
@@ -44263,7 +43685,7 @@
       </c>
       <c r="C43" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=16.59x taker=50.5445 ret=6.227931%</t>
+          <t>vol_vs_med14=15.81x taker=48.1466 ret=-27.631539%</t>
         </is>
       </c>
       <c r="D43" s="19" t="inlineStr">
@@ -44276,7 +43698,7 @@
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
@@ -44286,7 +43708,7 @@
       </c>
       <c r="C44" s="19" t="inlineStr">
         <is>
-          <t>vol_vs_med14=10.14x taker=51.3881 ret=41.019263%</t>
+          <t>vol_vs_med14=50.95x taker=49.8378 ret=19.854068%</t>
         </is>
       </c>
       <c r="D44" s="19" t="inlineStr">
@@ -44299,25 +43721,186 @@
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=16.59x taker=50.5445 ret=6.227931%</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C46" s="19" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=10.14x taker=51.3881 ret=41.019263%</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="B45" s="19" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>VOL_8X_MED14</t>
         </is>
       </c>
-      <c r="C45" s="19" t="inlineStr">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>vol_vs_med14=22.36x taker=50.2243 ret=-3.478546%</t>
         </is>
       </c>
-      <c r="D45" s="19" t="inlineStr">
+      <c r="D47" s="19" t="inlineStr">
         <is>
           <t>fapi_klines_1d</t>
         </is>
       </c>
-      <c r="E45" s="19" t="inlineStr"/>
+      <c r="E47" s="19" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C48" s="19" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=345.58x taker=None ret=192.30028874%</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=203.39x taker=None ret=-17.59960487%</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C50" s="19" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=60.59x taker=None ret=2.07792208%</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E50" s="19" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=63.46x taker=None ret=-68.29125073%</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>VOL_8X_MED14</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
+        <is>
+          <t>vol_vs_med14=41.82x taker=None ret=21.11111111%</t>
+        </is>
+      </c>
+      <c r="D52" s="19" t="inlineStr">
+        <is>
+          <t>fapi_klines_1d</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
